--- a/unitydata/excel/bigmap.xlsx
+++ b/unitydata/excel/bigmap.xlsx
@@ -4924,7 +4924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q519"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -4965,8 +4965,10 @@
       <c r="G1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>25</v>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>boss_reward</t>
+        </is>
       </c>
       <c r="I1" s="15" t="s">
         <v>733</v>
@@ -5009,8 +5011,10 @@
       <c r="G2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>29</v>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="I2" s="15" t="s">
         <v>734</v>
@@ -5053,8 +5057,10 @@
       <c r="G3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>26</v>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Boss通关宝箱奖励包ID</t>
+        </is>
       </c>
       <c r="I3" s="15" t="s">
         <v>735</v>
@@ -5097,8 +5103,10 @@
       <c r="G4" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>23</v>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
       <c r="I4" s="15" t="s">
         <v>736</v>
@@ -5137,8 +5145,8 @@
         <v>101</v>
       </c>
       <c r="G5" s="13"/>
-      <c r="H5" s="13" t="s">
-        <v>31</v>
+      <c r="H5" s="13" t="n">
+        <v>20013</v>
       </c>
       <c r="I5" s="12">
         <v>10001</v>
@@ -5177,8 +5185,8 @@
         <v>102</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="13" t="s">
-        <v>785</v>
+      <c r="H6" s="13" t="n">
+        <v>20023</v>
       </c>
       <c r="I6" s="12">
         <v>10011</v>
@@ -5217,8 +5225,8 @@
         <v>103</v>
       </c>
       <c r="G7" s="13"/>
-      <c r="H7" s="13" t="s">
-        <v>786</v>
+      <c r="H7" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I7" s="12">
         <v>10021</v>
@@ -5257,8 +5265,8 @@
         <v>104</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
-        <v>786</v>
+      <c r="H8" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I8" s="12">
         <v>10031</v>
@@ -5297,8 +5305,8 @@
         <v>105</v>
       </c>
       <c r="G9" s="13"/>
-      <c r="H9" s="13" t="s">
-        <v>786</v>
+      <c r="H9" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I9" s="12">
         <v>10041</v>
@@ -5337,8 +5345,8 @@
         <v>106</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="13" t="s">
-        <v>786</v>
+      <c r="H10" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="12">
@@ -5375,8 +5383,8 @@
         <v>107</v>
       </c>
       <c r="G11" s="13"/>
-      <c r="H11" s="13" t="s">
-        <v>786</v>
+      <c r="H11" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="12">
@@ -5413,8 +5421,8 @@
         <v>108</v>
       </c>
       <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
-        <v>786</v>
+      <c r="H12" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="12">
@@ -5451,8 +5459,8 @@
         <v>109</v>
       </c>
       <c r="G13" s="13"/>
-      <c r="H13" s="13" t="s">
-        <v>786</v>
+      <c r="H13" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="12">
@@ -5489,8 +5497,8 @@
         <v>110</v>
       </c>
       <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
-        <v>786</v>
+      <c r="H14" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="12">
@@ -5527,8 +5535,8 @@
         <v>111</v>
       </c>
       <c r="G15" s="13"/>
-      <c r="H15" s="13" t="s">
-        <v>786</v>
+      <c r="H15" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="12">
@@ -5565,8 +5573,8 @@
         <v>112</v>
       </c>
       <c r="G16" s="13"/>
-      <c r="H16" s="13" t="s">
-        <v>786</v>
+      <c r="H16" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="12">
@@ -5603,8 +5611,8 @@
         <v>113</v>
       </c>
       <c r="G17" s="13"/>
-      <c r="H17" s="13" t="s">
-        <v>786</v>
+      <c r="H17" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="12">
@@ -5641,8 +5649,8 @@
         <v>114</v>
       </c>
       <c r="G18" s="13"/>
-      <c r="H18" s="13" t="s">
-        <v>786</v>
+      <c r="H18" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="12">
@@ -5679,8 +5687,8 @@
         <v>115</v>
       </c>
       <c r="G19" s="13"/>
-      <c r="H19" s="13" t="s">
-        <v>786</v>
+      <c r="H19" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="12">
@@ -5717,8 +5725,8 @@
         <v>116</v>
       </c>
       <c r="G20" s="13"/>
-      <c r="H20" s="13" t="s">
-        <v>786</v>
+      <c r="H20" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="12">
@@ -5755,8 +5763,8 @@
         <v>117</v>
       </c>
       <c r="G21" s="13"/>
-      <c r="H21" s="13" t="s">
-        <v>786</v>
+      <c r="H21" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="12">
@@ -5796,8 +5804,8 @@
         <v>118</v>
       </c>
       <c r="G22" s="13"/>
-      <c r="H22" s="13" t="s">
-        <v>786</v>
+      <c r="H22" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="12">
@@ -5837,8 +5845,8 @@
         <v>119</v>
       </c>
       <c r="G23" s="13"/>
-      <c r="H23" s="13" t="s">
-        <v>786</v>
+      <c r="H23" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="12">
@@ -5878,8 +5886,8 @@
         <v>120</v>
       </c>
       <c r="G24" s="13"/>
-      <c r="H24" s="13" t="s">
-        <v>786</v>
+      <c r="H24" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="12">
@@ -5919,8 +5927,8 @@
         <v>121</v>
       </c>
       <c r="G25" s="13"/>
-      <c r="H25" s="13" t="s">
-        <v>786</v>
+      <c r="H25" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="12">
@@ -5960,8 +5968,8 @@
         <v>122</v>
       </c>
       <c r="G26" s="13"/>
-      <c r="H26" s="13" t="s">
-        <v>786</v>
+      <c r="H26" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="12">
@@ -6001,8 +6009,8 @@
         <v>123</v>
       </c>
       <c r="G27" s="13"/>
-      <c r="H27" s="13" t="s">
-        <v>786</v>
+      <c r="H27" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="12">
@@ -6042,8 +6050,8 @@
         <v>124</v>
       </c>
       <c r="G28" s="13"/>
-      <c r="H28" s="13" t="s">
-        <v>786</v>
+      <c r="H28" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="12">
@@ -6083,8 +6091,8 @@
         <v>125</v>
       </c>
       <c r="G29" s="13"/>
-      <c r="H29" s="13" t="s">
-        <v>786</v>
+      <c r="H29" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="12">
@@ -6121,8 +6129,8 @@
         <v>126</v>
       </c>
       <c r="G30" s="13"/>
-      <c r="H30" s="13" t="s">
-        <v>786</v>
+      <c r="H30" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="12">
@@ -6159,8 +6167,8 @@
         <v>127</v>
       </c>
       <c r="G31" s="13"/>
-      <c r="H31" s="13" t="s">
-        <v>786</v>
+      <c r="H31" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="12">
@@ -6197,8 +6205,8 @@
         <v>128</v>
       </c>
       <c r="G32" s="13"/>
-      <c r="H32" s="13" t="s">
-        <v>786</v>
+      <c r="H32" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I32" s="13"/>
       <c r="J32" s="12">
@@ -6235,8 +6243,8 @@
         <v>129</v>
       </c>
       <c r="G33" s="13"/>
-      <c r="H33" s="13" t="s">
-        <v>786</v>
+      <c r="H33" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="12">
@@ -6273,8 +6281,8 @@
         <v>130</v>
       </c>
       <c r="G34" s="13"/>
-      <c r="H34" s="13" t="s">
-        <v>786</v>
+      <c r="H34" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="12">
@@ -6311,8 +6319,8 @@
         <v>131</v>
       </c>
       <c r="G35" s="13"/>
-      <c r="H35" s="13" t="s">
-        <v>786</v>
+      <c r="H35" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="12">
@@ -6349,8 +6357,8 @@
         <v>132</v>
       </c>
       <c r="G36" s="13"/>
-      <c r="H36" s="13" t="s">
-        <v>786</v>
+      <c r="H36" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="12">
@@ -6387,8 +6395,8 @@
         <v>133</v>
       </c>
       <c r="G37" s="13"/>
-      <c r="H37" s="13" t="s">
-        <v>786</v>
+      <c r="H37" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="12">
@@ -6425,8 +6433,8 @@
         <v>134</v>
       </c>
       <c r="G38" s="13"/>
-      <c r="H38" s="13" t="s">
-        <v>786</v>
+      <c r="H38" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="12">
@@ -6463,8 +6471,8 @@
         <v>135</v>
       </c>
       <c r="G39" s="13"/>
-      <c r="H39" s="13" t="s">
-        <v>786</v>
+      <c r="H39" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="12">
@@ -6501,8 +6509,8 @@
         <v>136</v>
       </c>
       <c r="G40" s="13"/>
-      <c r="H40" s="13" t="s">
-        <v>786</v>
+      <c r="H40" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="12">
@@ -6539,8 +6547,8 @@
         <v>137</v>
       </c>
       <c r="G41" s="13"/>
-      <c r="H41" s="13" t="s">
-        <v>786</v>
+      <c r="H41" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="12">
@@ -6577,8 +6585,8 @@
         <v>138</v>
       </c>
       <c r="G42" s="13"/>
-      <c r="H42" s="13" t="s">
-        <v>786</v>
+      <c r="H42" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="12">
@@ -6615,8 +6623,8 @@
         <v>139</v>
       </c>
       <c r="G43" s="14"/>
-      <c r="H43" s="13" t="s">
-        <v>786</v>
+      <c r="H43" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="12">
@@ -6653,8 +6661,8 @@
         <v>140</v>
       </c>
       <c r="G44" s="14"/>
-      <c r="H44" s="13" t="s">
-        <v>786</v>
+      <c r="H44" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="12">
@@ -6691,8 +6699,8 @@
         <v>141</v>
       </c>
       <c r="G45" s="14"/>
-      <c r="H45" s="13" t="s">
-        <v>786</v>
+      <c r="H45" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="12">
@@ -6729,8 +6737,8 @@
         <v>142</v>
       </c>
       <c r="G46" s="14"/>
-      <c r="H46" s="13" t="s">
-        <v>786</v>
+      <c r="H46" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="12">
@@ -6767,8 +6775,8 @@
         <v>143</v>
       </c>
       <c r="G47" s="14"/>
-      <c r="H47" s="13" t="s">
-        <v>786</v>
+      <c r="H47" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="12">
@@ -6805,8 +6813,8 @@
         <v>144</v>
       </c>
       <c r="G48" s="14"/>
-      <c r="H48" s="13" t="s">
-        <v>786</v>
+      <c r="H48" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="12">
@@ -6843,8 +6851,8 @@
         <v>145</v>
       </c>
       <c r="G49" s="14"/>
-      <c r="H49" s="13" t="s">
-        <v>786</v>
+      <c r="H49" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="12">
@@ -6881,8 +6889,8 @@
         <v>146</v>
       </c>
       <c r="G50" s="14"/>
-      <c r="H50" s="13" t="s">
-        <v>786</v>
+      <c r="H50" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="12">
@@ -6919,8 +6927,8 @@
         <v>147</v>
       </c>
       <c r="G51" s="14"/>
-      <c r="H51" s="13" t="s">
-        <v>786</v>
+      <c r="H51" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="12">
@@ -6957,8 +6965,8 @@
         <v>148</v>
       </c>
       <c r="G52" s="14"/>
-      <c r="H52" s="13" t="s">
-        <v>786</v>
+      <c r="H52" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="12">
@@ -6995,8 +7003,8 @@
         <v>149</v>
       </c>
       <c r="G53" s="13"/>
-      <c r="H53" s="13" t="s">
-        <v>786</v>
+      <c r="H53" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="12">
@@ -7033,8 +7041,8 @@
         <v>150</v>
       </c>
       <c r="G54" s="13"/>
-      <c r="H54" s="13" t="s">
-        <v>786</v>
+      <c r="H54" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="12">
@@ -7071,8 +7079,8 @@
         <v>151</v>
       </c>
       <c r="G55" s="13"/>
-      <c r="H55" s="13" t="s">
-        <v>786</v>
+      <c r="H55" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="12">
@@ -7109,8 +7117,8 @@
         <v>152</v>
       </c>
       <c r="G56" s="13"/>
-      <c r="H56" s="13" t="s">
-        <v>786</v>
+      <c r="H56" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="12">
@@ -7147,8 +7155,8 @@
         <v>153</v>
       </c>
       <c r="G57" s="13"/>
-      <c r="H57" s="13" t="s">
-        <v>786</v>
+      <c r="H57" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="12">
@@ -7185,8 +7193,8 @@
         <v>154</v>
       </c>
       <c r="G58" s="13"/>
-      <c r="H58" s="13" t="s">
-        <v>786</v>
+      <c r="H58" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="12">
@@ -7223,8 +7231,8 @@
         <v>155</v>
       </c>
       <c r="G59" s="13"/>
-      <c r="H59" s="13" t="s">
-        <v>786</v>
+      <c r="H59" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="12">
@@ -7261,8 +7269,8 @@
         <v>156</v>
       </c>
       <c r="G60" s="13"/>
-      <c r="H60" s="13" t="s">
-        <v>786</v>
+      <c r="H60" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="12">
@@ -7299,8 +7307,8 @@
         <v>157</v>
       </c>
       <c r="G61" s="13"/>
-      <c r="H61" s="13" t="s">
-        <v>786</v>
+      <c r="H61" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="12">
@@ -7337,8 +7345,8 @@
         <v>158</v>
       </c>
       <c r="G62" s="13"/>
-      <c r="H62" s="13" t="s">
-        <v>786</v>
+      <c r="H62" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="12">
@@ -7375,8 +7383,8 @@
         <v>159</v>
       </c>
       <c r="G63" s="13"/>
-      <c r="H63" s="13" t="s">
-        <v>786</v>
+      <c r="H63" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="12">
@@ -7413,8 +7421,8 @@
         <v>160</v>
       </c>
       <c r="G64" s="13"/>
-      <c r="H64" s="13" t="s">
-        <v>786</v>
+      <c r="H64" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="12">
@@ -7451,8 +7459,8 @@
         <v>161</v>
       </c>
       <c r="G65" s="13"/>
-      <c r="H65" s="13" t="s">
-        <v>786</v>
+      <c r="H65" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="12">
@@ -7489,8 +7497,8 @@
         <v>162</v>
       </c>
       <c r="G66" s="13"/>
-      <c r="H66" s="13" t="s">
-        <v>786</v>
+      <c r="H66" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I66" s="13"/>
       <c r="J66" s="12">
@@ -7527,8 +7535,8 @@
         <v>163</v>
       </c>
       <c r="G67" s="13"/>
-      <c r="H67" s="13" t="s">
-        <v>786</v>
+      <c r="H67" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="12">
@@ -7565,8 +7573,8 @@
         <v>164</v>
       </c>
       <c r="G68" s="13"/>
-      <c r="H68" s="13" t="s">
-        <v>786</v>
+      <c r="H68" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="12">
@@ -7603,8 +7611,8 @@
         <v>165</v>
       </c>
       <c r="G69" s="13"/>
-      <c r="H69" s="13" t="s">
-        <v>786</v>
+      <c r="H69" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I69" s="13"/>
       <c r="J69" s="12">
@@ -7641,8 +7649,8 @@
         <v>166</v>
       </c>
       <c r="G70" s="13"/>
-      <c r="H70" s="13" t="s">
-        <v>786</v>
+      <c r="H70" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I70" s="13"/>
       <c r="J70" s="12">
@@ -7679,8 +7687,8 @@
         <v>167</v>
       </c>
       <c r="G71" s="13"/>
-      <c r="H71" s="13" t="s">
-        <v>786</v>
+      <c r="H71" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="12">
@@ -7717,8 +7725,8 @@
         <v>168</v>
       </c>
       <c r="G72" s="13"/>
-      <c r="H72" s="13" t="s">
-        <v>786</v>
+      <c r="H72" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I72" s="13"/>
       <c r="J72" s="12">
@@ -7755,8 +7763,8 @@
         <v>169</v>
       </c>
       <c r="G73" s="13"/>
-      <c r="H73" s="13" t="s">
-        <v>786</v>
+      <c r="H73" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I73" s="13"/>
       <c r="J73" s="12">
@@ -7793,8 +7801,8 @@
         <v>170</v>
       </c>
       <c r="G74" s="13"/>
-      <c r="H74" s="13" t="s">
-        <v>786</v>
+      <c r="H74" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I74" s="13"/>
       <c r="J74" s="12">
@@ -7831,8 +7839,8 @@
         <v>171</v>
       </c>
       <c r="G75" s="13"/>
-      <c r="H75" s="13" t="s">
-        <v>786</v>
+      <c r="H75" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I75" s="13"/>
       <c r="J75" s="12">
@@ -7869,8 +7877,8 @@
         <v>172</v>
       </c>
       <c r="G76" s="13"/>
-      <c r="H76" s="13" t="s">
-        <v>786</v>
+      <c r="H76" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="12">
@@ -7907,8 +7915,8 @@
         <v>173</v>
       </c>
       <c r="G77" s="13"/>
-      <c r="H77" s="13" t="s">
-        <v>786</v>
+      <c r="H77" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="12">
@@ -7945,8 +7953,8 @@
         <v>174</v>
       </c>
       <c r="G78" s="13"/>
-      <c r="H78" s="13" t="s">
-        <v>786</v>
+      <c r="H78" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="12">
@@ -7983,8 +7991,8 @@
         <v>175</v>
       </c>
       <c r="G79" s="13"/>
-      <c r="H79" s="13" t="s">
-        <v>786</v>
+      <c r="H79" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I79" s="13"/>
       <c r="J79" s="12">
@@ -8021,8 +8029,8 @@
         <v>176</v>
       </c>
       <c r="G80" s="13"/>
-      <c r="H80" s="13" t="s">
-        <v>786</v>
+      <c r="H80" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I80" s="13"/>
       <c r="J80" s="12">
@@ -8059,8 +8067,8 @@
         <v>177</v>
       </c>
       <c r="G81" s="13"/>
-      <c r="H81" s="13" t="s">
-        <v>786</v>
+      <c r="H81" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I81" s="13"/>
       <c r="J81" s="12">
@@ -8097,8 +8105,8 @@
         <v>178</v>
       </c>
       <c r="G82" s="13"/>
-      <c r="H82" s="13" t="s">
-        <v>786</v>
+      <c r="H82" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I82" s="13"/>
       <c r="J82" s="12">
@@ -8135,8 +8143,8 @@
         <v>179</v>
       </c>
       <c r="G83" s="13"/>
-      <c r="H83" s="13" t="s">
-        <v>786</v>
+      <c r="H83" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I83" s="13"/>
       <c r="J83" s="12">
@@ -8173,8 +8181,8 @@
         <v>180</v>
       </c>
       <c r="G84" s="13"/>
-      <c r="H84" s="13" t="s">
-        <v>786</v>
+      <c r="H84" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I84" s="13"/>
       <c r="J84" s="12">
@@ -8211,8 +8219,8 @@
         <v>181</v>
       </c>
       <c r="G85" s="13"/>
-      <c r="H85" s="13" t="s">
-        <v>786</v>
+      <c r="H85" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="12">
@@ -8249,8 +8257,8 @@
         <v>182</v>
       </c>
       <c r="G86" s="13"/>
-      <c r="H86" s="13" t="s">
-        <v>786</v>
+      <c r="H86" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I86" s="13"/>
       <c r="J86" s="12">
@@ -8287,8 +8295,8 @@
         <v>183</v>
       </c>
       <c r="G87" s="13"/>
-      <c r="H87" s="13" t="s">
-        <v>786</v>
+      <c r="H87" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I87" s="13"/>
       <c r="J87" s="12">
@@ -8325,8 +8333,8 @@
         <v>184</v>
       </c>
       <c r="G88" s="13"/>
-      <c r="H88" s="13" t="s">
-        <v>786</v>
+      <c r="H88" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I88" s="13"/>
       <c r="J88" s="12">
@@ -8363,8 +8371,8 @@
         <v>185</v>
       </c>
       <c r="G89" s="13"/>
-      <c r="H89" s="13" t="s">
-        <v>786</v>
+      <c r="H89" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I89" s="13"/>
       <c r="J89" s="12">
@@ -8401,8 +8409,8 @@
         <v>186</v>
       </c>
       <c r="G90" s="13"/>
-      <c r="H90" s="13" t="s">
-        <v>786</v>
+      <c r="H90" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I90" s="13"/>
       <c r="J90" s="12">
@@ -8439,8 +8447,8 @@
         <v>187</v>
       </c>
       <c r="G91" s="13"/>
-      <c r="H91" s="13" t="s">
-        <v>786</v>
+      <c r="H91" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I91" s="13"/>
       <c r="J91" s="12">
@@ -8477,8 +8485,8 @@
         <v>188</v>
       </c>
       <c r="G92" s="13"/>
-      <c r="H92" s="13" t="s">
-        <v>786</v>
+      <c r="H92" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I92" s="13"/>
       <c r="J92" s="12">
@@ -8515,8 +8523,8 @@
         <v>189</v>
       </c>
       <c r="G93" s="13"/>
-      <c r="H93" s="13" t="s">
-        <v>786</v>
+      <c r="H93" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I93" s="13"/>
       <c r="J93" s="12">
@@ -8553,8 +8561,8 @@
         <v>190</v>
       </c>
       <c r="G94" s="13"/>
-      <c r="H94" s="13" t="s">
-        <v>786</v>
+      <c r="H94" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I94" s="13"/>
       <c r="J94" s="12">
@@ -8591,8 +8599,8 @@
         <v>191</v>
       </c>
       <c r="G95" s="13"/>
-      <c r="H95" s="13" t="s">
-        <v>786</v>
+      <c r="H95" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="12">
@@ -8629,8 +8637,8 @@
         <v>192</v>
       </c>
       <c r="G96" s="13"/>
-      <c r="H96" s="13" t="s">
-        <v>786</v>
+      <c r="H96" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="12">
@@ -8667,8 +8675,8 @@
         <v>193</v>
       </c>
       <c r="G97" s="13"/>
-      <c r="H97" s="13" t="s">
-        <v>786</v>
+      <c r="H97" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="12">
@@ -8705,8 +8713,8 @@
         <v>194</v>
       </c>
       <c r="G98" s="13"/>
-      <c r="H98" s="13" t="s">
-        <v>786</v>
+      <c r="H98" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="12">
@@ -8743,8 +8751,8 @@
         <v>195</v>
       </c>
       <c r="G99" s="13"/>
-      <c r="H99" s="13" t="s">
-        <v>786</v>
+      <c r="H99" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="12">
@@ -8781,8 +8789,8 @@
         <v>196</v>
       </c>
       <c r="G100" s="13"/>
-      <c r="H100" s="13" t="s">
-        <v>786</v>
+      <c r="H100" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I100" s="13"/>
       <c r="J100" s="12">
@@ -8819,8 +8827,8 @@
         <v>197</v>
       </c>
       <c r="G101" s="13"/>
-      <c r="H101" s="13" t="s">
-        <v>786</v>
+      <c r="H101" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="12">
@@ -8857,8 +8865,8 @@
         <v>198</v>
       </c>
       <c r="G102" s="13"/>
-      <c r="H102" s="13" t="s">
-        <v>786</v>
+      <c r="H102" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="12">
@@ -8895,8 +8903,8 @@
         <v>199</v>
       </c>
       <c r="G103" s="13"/>
-      <c r="H103" s="13" t="s">
-        <v>786</v>
+      <c r="H103" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="12">
@@ -8933,8 +8941,8 @@
         <v>200</v>
       </c>
       <c r="G104" s="13"/>
-      <c r="H104" s="13" t="s">
-        <v>786</v>
+      <c r="H104" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="12">
@@ -8971,8 +8979,8 @@
         <v>201</v>
       </c>
       <c r="G105" s="13"/>
-      <c r="H105" s="13" t="s">
-        <v>786</v>
+      <c r="H105" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="12">
@@ -9009,8 +9017,8 @@
         <v>202</v>
       </c>
       <c r="G106" s="13"/>
-      <c r="H106" s="13" t="s">
-        <v>786</v>
+      <c r="H106" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="12">
@@ -9047,8 +9055,8 @@
         <v>203</v>
       </c>
       <c r="G107" s="13"/>
-      <c r="H107" s="13" t="s">
-        <v>786</v>
+      <c r="H107" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="12">
@@ -9085,8 +9093,8 @@
         <v>204</v>
       </c>
       <c r="G108" s="13"/>
-      <c r="H108" s="13" t="s">
-        <v>786</v>
+      <c r="H108" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="12">
@@ -9123,8 +9131,8 @@
         <v>205</v>
       </c>
       <c r="G109" s="13"/>
-      <c r="H109" s="13" t="s">
-        <v>786</v>
+      <c r="H109" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="12">
@@ -9161,8 +9169,8 @@
         <v>206</v>
       </c>
       <c r="G110" s="13"/>
-      <c r="H110" s="13" t="s">
-        <v>786</v>
+      <c r="H110" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="12">
@@ -9199,8 +9207,8 @@
         <v>207</v>
       </c>
       <c r="G111" s="13"/>
-      <c r="H111" s="13" t="s">
-        <v>786</v>
+      <c r="H111" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I111" s="13"/>
       <c r="J111" s="12">
@@ -9237,8 +9245,8 @@
         <v>208</v>
       </c>
       <c r="G112" s="13"/>
-      <c r="H112" s="13" t="s">
-        <v>786</v>
+      <c r="H112" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="12">
@@ -9275,8 +9283,8 @@
         <v>209</v>
       </c>
       <c r="G113" s="13"/>
-      <c r="H113" s="13" t="s">
-        <v>786</v>
+      <c r="H113" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="12">
@@ -9313,8 +9321,8 @@
         <v>210</v>
       </c>
       <c r="G114" s="13"/>
-      <c r="H114" s="13" t="s">
-        <v>786</v>
+      <c r="H114" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="12">
@@ -9351,8 +9359,8 @@
         <v>211</v>
       </c>
       <c r="G115" s="13"/>
-      <c r="H115" s="13" t="s">
-        <v>786</v>
+      <c r="H115" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I115" s="13"/>
       <c r="J115" s="12">
@@ -9389,8 +9397,8 @@
         <v>212</v>
       </c>
       <c r="G116" s="13"/>
-      <c r="H116" s="13" t="s">
-        <v>786</v>
+      <c r="H116" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I116" s="13"/>
       <c r="J116" s="12">
@@ -9427,8 +9435,8 @@
         <v>213</v>
       </c>
       <c r="G117" s="13"/>
-      <c r="H117" s="13" t="s">
-        <v>786</v>
+      <c r="H117" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I117" s="13"/>
       <c r="J117" s="12">
@@ -9465,8 +9473,8 @@
         <v>214</v>
       </c>
       <c r="G118" s="13"/>
-      <c r="H118" s="13" t="s">
-        <v>786</v>
+      <c r="H118" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I118" s="13"/>
       <c r="J118" s="12">
@@ -9503,8 +9511,8 @@
         <v>215</v>
       </c>
       <c r="G119" s="13"/>
-      <c r="H119" s="13" t="s">
-        <v>786</v>
+      <c r="H119" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I119" s="13"/>
       <c r="J119" s="12">
@@ -9541,8 +9549,8 @@
         <v>216</v>
       </c>
       <c r="G120" s="13"/>
-      <c r="H120" s="13" t="s">
-        <v>786</v>
+      <c r="H120" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I120" s="13"/>
       <c r="J120" s="12">
@@ -9579,8 +9587,8 @@
         <v>217</v>
       </c>
       <c r="G121" s="13"/>
-      <c r="H121" s="13" t="s">
-        <v>786</v>
+      <c r="H121" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="12">
@@ -9617,8 +9625,8 @@
         <v>218</v>
       </c>
       <c r="G122" s="13"/>
-      <c r="H122" s="13" t="s">
-        <v>786</v>
+      <c r="H122" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="12">
@@ -9655,8 +9663,8 @@
         <v>219</v>
       </c>
       <c r="G123" s="13"/>
-      <c r="H123" s="13" t="s">
-        <v>786</v>
+      <c r="H123" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="12">
@@ -9693,8 +9701,8 @@
         <v>220</v>
       </c>
       <c r="G124" s="13"/>
-      <c r="H124" s="13" t="s">
-        <v>786</v>
+      <c r="H124" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="12">
@@ -9731,8 +9739,8 @@
         <v>221</v>
       </c>
       <c r="G125" s="13"/>
-      <c r="H125" s="13" t="s">
-        <v>786</v>
+      <c r="H125" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I125" s="13"/>
       <c r="J125" s="12">
@@ -9769,8 +9777,8 @@
         <v>222</v>
       </c>
       <c r="G126" s="13"/>
-      <c r="H126" s="13" t="s">
-        <v>786</v>
+      <c r="H126" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I126" s="13"/>
       <c r="J126" s="12">
@@ -9807,8 +9815,8 @@
         <v>223</v>
       </c>
       <c r="G127" s="13"/>
-      <c r="H127" s="13" t="s">
-        <v>786</v>
+      <c r="H127" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I127" s="13"/>
       <c r="J127" s="12">
@@ -9845,8 +9853,8 @@
         <v>224</v>
       </c>
       <c r="G128" s="13"/>
-      <c r="H128" s="13" t="s">
-        <v>786</v>
+      <c r="H128" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I128" s="13"/>
       <c r="J128" s="12">
@@ -9883,8 +9891,8 @@
         <v>225</v>
       </c>
       <c r="G129" s="13"/>
-      <c r="H129" s="13" t="s">
-        <v>786</v>
+      <c r="H129" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I129" s="13"/>
       <c r="J129" s="12">
@@ -9921,8 +9929,8 @@
         <v>226</v>
       </c>
       <c r="G130" s="13"/>
-      <c r="H130" s="13" t="s">
-        <v>786</v>
+      <c r="H130" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I130" s="13"/>
       <c r="J130" s="12">
@@ -9959,8 +9967,8 @@
         <v>227</v>
       </c>
       <c r="G131" s="13"/>
-      <c r="H131" s="13" t="s">
-        <v>786</v>
+      <c r="H131" s="13" t="n">
+        <v>20033</v>
       </c>
       <c r="I131" s="13"/>
       <c r="J131" s="12">
@@ -9997,7 +10005,9 @@
         <v>0</v>
       </c>
       <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
+      <c r="H132" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
@@ -10022,7 +10032,9 @@
         <v>0</v>
       </c>
       <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
+      <c r="H133" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
       <c r="K133" s="6"/>
@@ -10047,7 +10059,9 @@
         <v>0</v>
       </c>
       <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
+      <c r="H134" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
       <c r="K134" s="6"/>
@@ -10074,7 +10088,9 @@
       <c r="G135" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H135" s="9"/>
+      <c r="H135" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
       <c r="K135" s="6"/>
@@ -10101,7 +10117,9 @@
       <c r="G136" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H136" s="9"/>
+      <c r="H136" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
@@ -10128,7 +10146,9 @@
       <c r="G137" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H137" s="9"/>
+      <c r="H137" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
@@ -10155,7 +10175,9 @@
       <c r="G138" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H138" s="9"/>
+      <c r="H138" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
       <c r="K138" s="6"/>
@@ -10182,7 +10204,9 @@
         <v>0</v>
       </c>
       <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
+      <c r="H139" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
       <c r="K139" s="6"/>
@@ -10209,7 +10233,9 @@
         <v>0</v>
       </c>
       <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
+      <c r="H140" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
@@ -10235,7 +10261,9 @@
         <v>0</v>
       </c>
       <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
+      <c r="H141" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
@@ -10261,7 +10289,9 @@
         <v>0</v>
       </c>
       <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
+      <c r="H142" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
       <c r="K142" s="6"/>
@@ -10287,7 +10317,9 @@
         <v>0</v>
       </c>
       <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
+      <c r="H143" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
@@ -10313,7 +10345,9 @@
         <v>0</v>
       </c>
       <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
+      <c r="H144" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
       <c r="K144" s="6"/>
@@ -10339,7 +10373,9 @@
         <v>0</v>
       </c>
       <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
+      <c r="H145" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
       <c r="K145" s="6"/>
@@ -10365,7 +10401,9 @@
         <v>0</v>
       </c>
       <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
+      <c r="H146" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
       <c r="K146" s="6"/>
@@ -10391,7 +10429,9 @@
         <v>0</v>
       </c>
       <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
+      <c r="H147" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
       <c r="K147" s="6"/>
@@ -10417,7 +10457,9 @@
         <v>0</v>
       </c>
       <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
+      <c r="H148" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
       <c r="K148" s="6"/>
@@ -10443,7 +10485,9 @@
         <v>0</v>
       </c>
       <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
+      <c r="H149" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
@@ -10469,7 +10513,9 @@
         <v>0</v>
       </c>
       <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
+      <c r="H150" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
       <c r="K150" s="6"/>
@@ -10495,7 +10541,9 @@
         <v>0</v>
       </c>
       <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
+      <c r="H151" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
       <c r="K151" s="6"/>
@@ -10521,7 +10569,9 @@
         <v>0</v>
       </c>
       <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
+      <c r="H152" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
@@ -10547,7 +10597,9 @@
         <v>0</v>
       </c>
       <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
+      <c r="H153" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
@@ -10573,7 +10625,9 @@
         <v>0</v>
       </c>
       <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
+      <c r="H154" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
       <c r="K154" s="6"/>
@@ -10599,7 +10653,9 @@
         <v>0</v>
       </c>
       <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
+      <c r="H155" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
       <c r="K155" s="6"/>
@@ -10625,7 +10681,9 @@
         <v>0</v>
       </c>
       <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
+      <c r="H156" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
@@ -10651,7 +10709,9 @@
         <v>0</v>
       </c>
       <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
+      <c r="H157" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
@@ -10677,7 +10737,9 @@
         <v>0</v>
       </c>
       <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
+      <c r="H158" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
@@ -10703,7 +10765,9 @@
         <v>0</v>
       </c>
       <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
+      <c r="H159" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
       <c r="K159" s="6"/>
@@ -10729,7 +10793,9 @@
         <v>0</v>
       </c>
       <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
+      <c r="H160" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
@@ -10755,7 +10821,9 @@
         <v>0</v>
       </c>
       <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
+      <c r="H161" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
@@ -10781,7 +10849,9 @@
         <v>0</v>
       </c>
       <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
+      <c r="H162" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
@@ -10807,7 +10877,9 @@
         <v>0</v>
       </c>
       <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
+      <c r="H163" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
       <c r="K163" s="6"/>
@@ -10833,7 +10905,9 @@
         <v>0</v>
       </c>
       <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
+      <c r="H164" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
       <c r="K164" s="6"/>
@@ -10859,7 +10933,9 @@
         <v>0</v>
       </c>
       <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
+      <c r="H165" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
       <c r="K165" s="6"/>
@@ -10885,7 +10961,9 @@
         <v>0</v>
       </c>
       <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
+      <c r="H166" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
       <c r="K166" s="6"/>
@@ -10911,7 +10989,9 @@
         <v>0</v>
       </c>
       <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
       <c r="K167" s="6"/>
@@ -10937,7 +11017,9 @@
         <v>0</v>
       </c>
       <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
+      <c r="H168" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
       <c r="K168" s="6"/>
@@ -10963,7 +11045,9 @@
         <v>0</v>
       </c>
       <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
+      <c r="H169" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
       <c r="K169" s="6"/>
@@ -10989,7 +11073,9 @@
         <v>0</v>
       </c>
       <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
+      <c r="H170" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
@@ -11015,7 +11101,9 @@
         <v>0</v>
       </c>
       <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
+      <c r="H171" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
       <c r="K171" s="6"/>
@@ -11041,7 +11129,9 @@
         <v>0</v>
       </c>
       <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
+      <c r="H172" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
       <c r="K172" s="6"/>
@@ -11067,7 +11157,9 @@
         <v>0</v>
       </c>
       <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
+      <c r="H173" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
       <c r="K173" s="6"/>
@@ -11093,7 +11185,9 @@
         <v>0</v>
       </c>
       <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
+      <c r="H174" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
@@ -11119,7 +11213,9 @@
         <v>0</v>
       </c>
       <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
+      <c r="H175" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
@@ -11145,7 +11241,9 @@
         <v>0</v>
       </c>
       <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
+      <c r="H176" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
       <c r="K176" s="6"/>
@@ -11171,7 +11269,9 @@
         <v>0</v>
       </c>
       <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
+      <c r="H177" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
       <c r="K177" s="6"/>
@@ -11197,7 +11297,9 @@
         <v>0</v>
       </c>
       <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
+      <c r="H178" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
@@ -11223,7 +11325,9 @@
         <v>0</v>
       </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
+      <c r="H179" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
       <c r="K179" s="6"/>
@@ -11249,7 +11353,9 @@
         <v>0</v>
       </c>
       <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
+      <c r="H180" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
@@ -11275,7 +11381,9 @@
         <v>0</v>
       </c>
       <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
+      <c r="H181" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
@@ -11301,7 +11409,9 @@
         <v>0</v>
       </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
+      <c r="H182" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
@@ -11327,7 +11437,9 @@
         <v>0</v>
       </c>
       <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
+      <c r="H183" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
@@ -11353,7 +11465,9 @@
         <v>0</v>
       </c>
       <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
+      <c r="H184" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
@@ -11377,7 +11491,9 @@
         <v>0</v>
       </c>
       <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
+      <c r="H185" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
@@ -11401,7 +11517,9 @@
         <v>0</v>
       </c>
       <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
+      <c r="H186" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
@@ -11425,7 +11543,9 @@
         <v>0</v>
       </c>
       <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
+      <c r="H187" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
@@ -11449,7 +11569,9 @@
         <v>0</v>
       </c>
       <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
+      <c r="H188" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
@@ -11473,7 +11595,9 @@
         <v>0</v>
       </c>
       <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
+      <c r="H189" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
@@ -11497,7 +11621,9 @@
         <v>0</v>
       </c>
       <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
+      <c r="H190" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
@@ -11521,7 +11647,9 @@
         <v>0</v>
       </c>
       <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
+      <c r="H191" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
@@ -11545,7 +11673,9 @@
         <v>0</v>
       </c>
       <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
+      <c r="H192" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
@@ -11569,7 +11699,9 @@
         <v>0</v>
       </c>
       <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
+      <c r="H193" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
@@ -11593,7 +11725,9 @@
         <v>0</v>
       </c>
       <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
+      <c r="H194" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
@@ -11617,7 +11751,9 @@
         <v>0</v>
       </c>
       <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
+      <c r="H195" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
@@ -11641,7 +11777,9 @@
         <v>0</v>
       </c>
       <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
+      <c r="H196" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
@@ -11667,7 +11805,9 @@
         <v>0</v>
       </c>
       <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
+      <c r="H197" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I197" s="6"/>
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
@@ -11691,7 +11831,9 @@
         <v>0</v>
       </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
+      <c r="H198" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I198" s="6"/>
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
@@ -11715,7 +11857,9 @@
         <v>0</v>
       </c>
       <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
+      <c r="H199" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I199" s="6"/>
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
@@ -11739,7 +11883,9 @@
         <v>0</v>
       </c>
       <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
+      <c r="H200" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I200" s="6"/>
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
@@ -11763,7 +11909,9 @@
         <v>0</v>
       </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
+      <c r="H201" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I201" s="6"/>
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
@@ -11787,7 +11935,9 @@
         <v>0</v>
       </c>
       <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
+      <c r="H202" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I202" s="6"/>
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
@@ -11811,7 +11961,9 @@
         <v>0</v>
       </c>
       <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
+      <c r="H203" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I203" s="6"/>
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
@@ -11837,7 +11989,9 @@
         <v>0</v>
       </c>
       <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
+      <c r="H204" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I204" s="6"/>
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
@@ -11863,7 +12017,9 @@
         <v>0</v>
       </c>
       <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
+      <c r="H205" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I205" s="6"/>
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
@@ -11889,7 +12045,9 @@
         <v>0</v>
       </c>
       <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
+      <c r="H206" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I206" s="6"/>
       <c r="J206" s="6"/>
       <c r="K206" s="6"/>
@@ -11915,7 +12073,9 @@
         <v>0</v>
       </c>
       <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
+      <c r="H207" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I207" s="6"/>
       <c r="J207" s="6"/>
       <c r="K207" s="6"/>
@@ -11941,7 +12101,9 @@
         <v>0</v>
       </c>
       <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
+      <c r="H208" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I208" s="6"/>
       <c r="J208" s="6"/>
       <c r="K208" s="6"/>
@@ -11967,7 +12129,9 @@
         <v>0</v>
       </c>
       <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
+      <c r="H209" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I209" s="6"/>
       <c r="J209" s="6"/>
       <c r="K209" s="6"/>
@@ -11993,7 +12157,9 @@
         <v>0</v>
       </c>
       <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
+      <c r="H210" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
       <c r="K210" s="6"/>
@@ -12019,7 +12185,9 @@
         <v>0</v>
       </c>
       <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
+      <c r="H211" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I211" s="6"/>
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
@@ -12045,7 +12213,9 @@
         <v>0</v>
       </c>
       <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
+      <c r="H212" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
       <c r="K212" s="6"/>
@@ -12071,7 +12241,9 @@
         <v>0</v>
       </c>
       <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
+      <c r="H213" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
@@ -12097,7 +12269,9 @@
         <v>0</v>
       </c>
       <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
+      <c r="H214" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
@@ -12123,7 +12297,9 @@
         <v>0</v>
       </c>
       <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
+      <c r="H215" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
       <c r="K215" s="6"/>
@@ -12149,7 +12325,9 @@
         <v>0</v>
       </c>
       <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
+      <c r="H216" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
       <c r="K216" s="6"/>
@@ -12175,7 +12353,9 @@
         <v>0</v>
       </c>
       <c r="G217" s="6"/>
-      <c r="H217" s="6"/>
+      <c r="H217" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
       <c r="K217" s="6"/>
@@ -12201,7 +12381,9 @@
         <v>0</v>
       </c>
       <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
+      <c r="H218" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
@@ -12227,7 +12409,9 @@
         <v>0</v>
       </c>
       <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
+      <c r="H219" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
@@ -12253,7 +12437,9 @@
         <v>0</v>
       </c>
       <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
+      <c r="H220" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I220" s="6"/>
       <c r="J220" s="6"/>
       <c r="K220" s="6"/>
@@ -12279,7 +12465,9 @@
         <v>0</v>
       </c>
       <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
+      <c r="H221" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I221" s="6"/>
       <c r="J221" s="6"/>
       <c r="K221" s="6"/>
@@ -12305,7 +12493,9 @@
         <v>0</v>
       </c>
       <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
+      <c r="H222" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I222" s="6"/>
       <c r="J222" s="6"/>
       <c r="K222" s="6"/>
@@ -12331,7 +12521,9 @@
         <v>0</v>
       </c>
       <c r="G223" s="6"/>
-      <c r="H223" s="6"/>
+      <c r="H223" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I223" s="6"/>
       <c r="J223" s="6"/>
       <c r="K223" s="6"/>
@@ -12357,7 +12549,9 @@
         <v>0</v>
       </c>
       <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
+      <c r="H224" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I224" s="6"/>
       <c r="J224" s="6"/>
       <c r="K224" s="6"/>
@@ -12383,7 +12577,9 @@
         <v>0</v>
       </c>
       <c r="G225" s="6"/>
-      <c r="H225" s="6"/>
+      <c r="H225" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I225" s="6"/>
       <c r="J225" s="6"/>
       <c r="K225" s="6"/>
@@ -12409,7 +12605,9 @@
         <v>0</v>
       </c>
       <c r="G226" s="6"/>
-      <c r="H226" s="6"/>
+      <c r="H226" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I226" s="6"/>
       <c r="J226" s="6"/>
       <c r="K226" s="6"/>
@@ -12435,7 +12633,9 @@
         <v>0</v>
       </c>
       <c r="G227" s="6"/>
-      <c r="H227" s="6"/>
+      <c r="H227" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I227" s="6"/>
       <c r="J227" s="6"/>
       <c r="K227" s="6"/>
@@ -12461,7 +12661,9 @@
         <v>0</v>
       </c>
       <c r="G228" s="6"/>
-      <c r="H228" s="6"/>
+      <c r="H228" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I228" s="6"/>
       <c r="J228" s="6"/>
       <c r="K228" s="6"/>
@@ -12487,7 +12689,9 @@
         <v>0</v>
       </c>
       <c r="G229" s="6"/>
-      <c r="H229" s="6"/>
+      <c r="H229" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I229" s="6"/>
       <c r="J229" s="6"/>
       <c r="K229" s="6"/>
@@ -12513,7 +12717,9 @@
         <v>0</v>
       </c>
       <c r="G230" s="6"/>
-      <c r="H230" s="6"/>
+      <c r="H230" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I230" s="6"/>
       <c r="J230" s="6"/>
       <c r="K230" s="6"/>
@@ -12539,7 +12745,9 @@
         <v>0</v>
       </c>
       <c r="G231" s="6"/>
-      <c r="H231" s="6"/>
+      <c r="H231" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I231" s="6"/>
       <c r="J231" s="6"/>
       <c r="K231" s="6"/>
@@ -12565,7 +12773,9 @@
         <v>0</v>
       </c>
       <c r="G232" s="6"/>
-      <c r="H232" s="6"/>
+      <c r="H232" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I232" s="6"/>
       <c r="J232" s="6"/>
       <c r="K232" s="6"/>
@@ -12591,7 +12801,9 @@
         <v>0</v>
       </c>
       <c r="G233" s="6"/>
-      <c r="H233" s="6"/>
+      <c r="H233" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I233" s="6"/>
       <c r="J233" s="6"/>
       <c r="K233" s="6"/>
@@ -12617,7 +12829,9 @@
         <v>0</v>
       </c>
       <c r="G234" s="6"/>
-      <c r="H234" s="6"/>
+      <c r="H234" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I234" s="6"/>
       <c r="J234" s="6"/>
       <c r="K234" s="6"/>
@@ -12643,7 +12857,9 @@
         <v>0</v>
       </c>
       <c r="G235" s="6"/>
-      <c r="H235" s="6"/>
+      <c r="H235" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I235" s="6"/>
       <c r="J235" s="6"/>
       <c r="K235" s="6"/>
@@ -12669,7 +12885,9 @@
         <v>0</v>
       </c>
       <c r="G236" s="6"/>
-      <c r="H236" s="6"/>
+      <c r="H236" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I236" s="6"/>
       <c r="J236" s="6"/>
       <c r="K236" s="6"/>
@@ -12695,7 +12913,9 @@
         <v>0</v>
       </c>
       <c r="G237" s="6"/>
-      <c r="H237" s="6"/>
+      <c r="H237" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I237" s="6"/>
       <c r="J237" s="6"/>
       <c r="K237" s="6"/>
@@ -12721,7 +12941,9 @@
         <v>0</v>
       </c>
       <c r="G238" s="6"/>
-      <c r="H238" s="6"/>
+      <c r="H238" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I238" s="6"/>
       <c r="J238" s="6"/>
       <c r="K238" s="6"/>
@@ -12747,7 +12969,9 @@
         <v>0</v>
       </c>
       <c r="G239" s="6"/>
-      <c r="H239" s="6"/>
+      <c r="H239" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I239" s="6"/>
       <c r="J239" s="6"/>
       <c r="K239" s="6"/>
@@ -12773,7 +12997,9 @@
         <v>0</v>
       </c>
       <c r="G240" s="6"/>
-      <c r="H240" s="6"/>
+      <c r="H240" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I240" s="6"/>
       <c r="J240" s="6"/>
       <c r="K240" s="6"/>
@@ -12799,7 +13025,9 @@
         <v>0</v>
       </c>
       <c r="G241" s="6"/>
-      <c r="H241" s="6"/>
+      <c r="H241" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I241" s="6"/>
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
@@ -12825,7 +13053,9 @@
         <v>0</v>
       </c>
       <c r="G242" s="6"/>
-      <c r="H242" s="6"/>
+      <c r="H242" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I242" s="6"/>
       <c r="J242" s="6"/>
       <c r="K242" s="6"/>
@@ -12851,7 +13081,9 @@
         <v>0</v>
       </c>
       <c r="G243" s="6"/>
-      <c r="H243" s="6"/>
+      <c r="H243" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I243" s="6"/>
       <c r="J243" s="6"/>
       <c r="K243" s="6"/>
@@ -12877,7 +13109,9 @@
         <v>0</v>
       </c>
       <c r="G244" s="6"/>
-      <c r="H244" s="6"/>
+      <c r="H244" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I244" s="6"/>
       <c r="J244" s="6"/>
       <c r="K244" s="6"/>
@@ -12903,7 +13137,9 @@
         <v>0</v>
       </c>
       <c r="G245" s="6"/>
-      <c r="H245" s="6"/>
+      <c r="H245" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I245" s="6"/>
       <c r="J245" s="6"/>
       <c r="K245" s="6"/>
@@ -12929,7 +13165,9 @@
         <v>0</v>
       </c>
       <c r="G246" s="6"/>
-      <c r="H246" s="6"/>
+      <c r="H246" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I246" s="6"/>
       <c r="J246" s="6"/>
       <c r="K246" s="6"/>
@@ -12955,7 +13193,9 @@
         <v>0</v>
       </c>
       <c r="G247" s="6"/>
-      <c r="H247" s="6"/>
+      <c r="H247" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I247" s="6"/>
       <c r="J247" s="6"/>
       <c r="K247" s="6"/>
@@ -12981,7 +13221,9 @@
         <v>0</v>
       </c>
       <c r="G248" s="6"/>
-      <c r="H248" s="6"/>
+      <c r="H248" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
@@ -13007,7 +13249,9 @@
         <v>0</v>
       </c>
       <c r="G249" s="6"/>
-      <c r="H249" s="6"/>
+      <c r="H249" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
       <c r="K249" s="6"/>
@@ -13033,7 +13277,9 @@
         <v>0</v>
       </c>
       <c r="G250" s="6"/>
-      <c r="H250" s="6"/>
+      <c r="H250" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I250" s="6"/>
       <c r="J250" s="6"/>
       <c r="K250" s="6"/>
@@ -13059,7 +13305,9 @@
         <v>0</v>
       </c>
       <c r="G251" s="6"/>
-      <c r="H251" s="6"/>
+      <c r="H251" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I251" s="6"/>
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
@@ -13085,7 +13333,9 @@
         <v>0</v>
       </c>
       <c r="G252" s="6"/>
-      <c r="H252" s="6"/>
+      <c r="H252" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I252" s="6"/>
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
@@ -13111,7 +13361,9 @@
         <v>0</v>
       </c>
       <c r="G253" s="6"/>
-      <c r="H253" s="6"/>
+      <c r="H253" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I253" s="6"/>
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
@@ -13137,7 +13389,9 @@
         <v>0</v>
       </c>
       <c r="G254" s="6"/>
-      <c r="H254" s="6"/>
+      <c r="H254" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I254" s="6"/>
       <c r="J254" s="6"/>
       <c r="K254" s="6"/>
@@ -13163,7 +13417,9 @@
         <v>0</v>
       </c>
       <c r="G255" s="6"/>
-      <c r="H255" s="6"/>
+      <c r="H255" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
       <c r="K255" s="6"/>
@@ -13189,7 +13445,9 @@
         <v>0</v>
       </c>
       <c r="G256" s="6"/>
-      <c r="H256" s="6"/>
+      <c r="H256" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
       <c r="K256" s="6"/>
@@ -13215,7 +13473,9 @@
         <v>0</v>
       </c>
       <c r="G257" s="6"/>
-      <c r="H257" s="6"/>
+      <c r="H257" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
       <c r="K257" s="6"/>
@@ -13241,7 +13501,9 @@
         <v>0</v>
       </c>
       <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
+      <c r="H258" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I258" s="6"/>
       <c r="J258" s="6"/>
       <c r="K258" s="6"/>
@@ -13267,7 +13529,9 @@
         <v>0</v>
       </c>
       <c r="G259" s="6"/>
-      <c r="H259" s="6"/>
+      <c r="H259" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I259" s="6"/>
       <c r="J259" s="6"/>
       <c r="K259" s="6"/>
@@ -13293,7 +13557,9 @@
         <v>0</v>
       </c>
       <c r="G260" s="6"/>
-      <c r="H260" s="6"/>
+      <c r="H260" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I260" s="6"/>
       <c r="J260" s="6"/>
       <c r="K260" s="6"/>
@@ -13319,7 +13585,9 @@
         <v>0</v>
       </c>
       <c r="G261" s="6"/>
-      <c r="H261" s="6"/>
+      <c r="H261" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I261" s="6"/>
       <c r="J261" s="6"/>
       <c r="K261" s="6"/>
@@ -13345,7 +13613,9 @@
         <v>0</v>
       </c>
       <c r="G262" s="6"/>
-      <c r="H262" s="6"/>
+      <c r="H262" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I262" s="6"/>
       <c r="J262" s="6"/>
       <c r="K262" s="6"/>
@@ -13371,7 +13641,9 @@
         <v>0</v>
       </c>
       <c r="G263" s="6"/>
-      <c r="H263" s="6"/>
+      <c r="H263" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I263" s="6"/>
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
@@ -13397,7 +13669,9 @@
         <v>0</v>
       </c>
       <c r="G264" s="6"/>
-      <c r="H264" s="6"/>
+      <c r="H264" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I264" s="6"/>
       <c r="J264" s="6"/>
       <c r="K264" s="6"/>
@@ -13423,7 +13697,9 @@
         <v>0</v>
       </c>
       <c r="G265" s="6"/>
-      <c r="H265" s="6"/>
+      <c r="H265" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
       <c r="K265" s="6"/>
@@ -13449,7 +13725,9 @@
         <v>0</v>
       </c>
       <c r="G266" s="6"/>
-      <c r="H266" s="6"/>
+      <c r="H266" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I266" s="6"/>
       <c r="J266" s="6"/>
       <c r="K266" s="6"/>
@@ -13475,7 +13753,9 @@
         <v>0</v>
       </c>
       <c r="G267" s="6"/>
-      <c r="H267" s="6"/>
+      <c r="H267" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I267" s="6"/>
       <c r="J267" s="6"/>
       <c r="K267" s="6"/>
@@ -13501,7 +13781,9 @@
         <v>0</v>
       </c>
       <c r="G268" s="6"/>
-      <c r="H268" s="6"/>
+      <c r="H268" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I268" s="6"/>
       <c r="J268" s="6"/>
       <c r="K268" s="6"/>
@@ -13527,7 +13809,9 @@
         <v>0</v>
       </c>
       <c r="G269" s="6"/>
-      <c r="H269" s="6"/>
+      <c r="H269" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I269" s="6"/>
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
@@ -13553,7 +13837,9 @@
         <v>0</v>
       </c>
       <c r="G270" s="6"/>
-      <c r="H270" s="6"/>
+      <c r="H270" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I270" s="6"/>
       <c r="J270" s="6"/>
       <c r="K270" s="6"/>
@@ -13579,7 +13865,9 @@
         <v>0</v>
       </c>
       <c r="G271" s="6"/>
-      <c r="H271" s="6"/>
+      <c r="H271" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I271" s="6"/>
       <c r="J271" s="6"/>
       <c r="K271" s="6"/>
@@ -13605,7 +13893,9 @@
         <v>0</v>
       </c>
       <c r="G272" s="6"/>
-      <c r="H272" s="6"/>
+      <c r="H272" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I272" s="6"/>
       <c r="J272" s="6"/>
       <c r="K272" s="6"/>
@@ -13631,7 +13921,9 @@
         <v>0</v>
       </c>
       <c r="G273" s="6"/>
-      <c r="H273" s="6"/>
+      <c r="H273" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I273" s="6"/>
       <c r="J273" s="6"/>
       <c r="K273" s="6"/>
@@ -13657,7 +13949,9 @@
         <v>0</v>
       </c>
       <c r="G274" s="6"/>
-      <c r="H274" s="6"/>
+      <c r="H274" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I274" s="6"/>
       <c r="J274" s="6"/>
       <c r="K274" s="6"/>
@@ -13683,7 +13977,9 @@
         <v>0</v>
       </c>
       <c r="G275" s="6"/>
-      <c r="H275" s="6"/>
+      <c r="H275" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I275" s="6"/>
       <c r="J275" s="6"/>
       <c r="K275" s="6"/>
@@ -13709,7 +14005,9 @@
         <v>0</v>
       </c>
       <c r="G276" s="6"/>
-      <c r="H276" s="6"/>
+      <c r="H276" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I276" s="6"/>
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
@@ -13735,7 +14033,9 @@
         <v>0</v>
       </c>
       <c r="G277" s="6"/>
-      <c r="H277" s="6"/>
+      <c r="H277" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I277" s="6"/>
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
@@ -13761,7 +14061,9 @@
         <v>0</v>
       </c>
       <c r="G278" s="6"/>
-      <c r="H278" s="6"/>
+      <c r="H278" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I278" s="6"/>
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
@@ -13787,7 +14089,9 @@
         <v>0</v>
       </c>
       <c r="G279" s="6"/>
-      <c r="H279" s="6"/>
+      <c r="H279" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I279" s="6"/>
       <c r="J279" s="6"/>
       <c r="K279" s="6"/>
@@ -13813,7 +14117,9 @@
         <v>0</v>
       </c>
       <c r="G280" s="6"/>
-      <c r="H280" s="6"/>
+      <c r="H280" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I280" s="6"/>
       <c r="J280" s="6"/>
       <c r="K280" s="6"/>
@@ -13839,7 +14145,9 @@
         <v>0</v>
       </c>
       <c r="G281" s="6"/>
-      <c r="H281" s="6"/>
+      <c r="H281" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I281" s="6"/>
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
@@ -13865,7 +14173,9 @@
         <v>0</v>
       </c>
       <c r="G282" s="6"/>
-      <c r="H282" s="6"/>
+      <c r="H282" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I282" s="6"/>
       <c r="J282" s="6"/>
       <c r="K282" s="6"/>
@@ -13891,7 +14201,9 @@
         <v>0</v>
       </c>
       <c r="G283" s="6"/>
-      <c r="H283" s="6"/>
+      <c r="H283" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I283" s="6"/>
       <c r="J283" s="6"/>
       <c r="K283" s="6"/>
@@ -13917,7 +14229,9 @@
         <v>0</v>
       </c>
       <c r="G284" s="6"/>
-      <c r="H284" s="6"/>
+      <c r="H284" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I284" s="6"/>
       <c r="J284" s="6"/>
       <c r="K284" s="6"/>
@@ -13943,7 +14257,9 @@
         <v>0</v>
       </c>
       <c r="G285" s="6"/>
-      <c r="H285" s="6"/>
+      <c r="H285" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I285" s="6"/>
       <c r="J285" s="6"/>
       <c r="K285" s="6"/>
@@ -13969,7 +14285,9 @@
         <v>0</v>
       </c>
       <c r="G286" s="6"/>
-      <c r="H286" s="6"/>
+      <c r="H286" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I286" s="6"/>
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
@@ -13995,7 +14313,9 @@
         <v>0</v>
       </c>
       <c r="G287" s="6"/>
-      <c r="H287" s="6"/>
+      <c r="H287" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I287" s="6"/>
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
@@ -14021,7 +14341,9 @@
         <v>0</v>
       </c>
       <c r="G288" s="6"/>
-      <c r="H288" s="6"/>
+      <c r="H288" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I288" s="6"/>
       <c r="J288" s="6"/>
       <c r="K288" s="6"/>
@@ -14047,7 +14369,9 @@
         <v>0</v>
       </c>
       <c r="G289" s="6"/>
-      <c r="H289" s="6"/>
+      <c r="H289" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I289" s="6"/>
       <c r="J289" s="6"/>
       <c r="K289" s="6"/>
@@ -14073,7 +14397,9 @@
         <v>0</v>
       </c>
       <c r="G290" s="6"/>
-      <c r="H290" s="6"/>
+      <c r="H290" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I290" s="6"/>
       <c r="J290" s="6"/>
       <c r="K290" s="6"/>
@@ -14099,7 +14425,9 @@
         <v>0</v>
       </c>
       <c r="G291" s="6"/>
-      <c r="H291" s="6"/>
+      <c r="H291" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I291" s="6"/>
       <c r="J291" s="6"/>
       <c r="K291" s="6"/>
@@ -14125,7 +14453,9 @@
         <v>0</v>
       </c>
       <c r="G292" s="6"/>
-      <c r="H292" s="6"/>
+      <c r="H292" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I292" s="6"/>
       <c r="J292" s="6"/>
       <c r="K292" s="6"/>
@@ -14151,7 +14481,9 @@
         <v>0</v>
       </c>
       <c r="G293" s="6"/>
-      <c r="H293" s="6"/>
+      <c r="H293" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I293" s="6"/>
       <c r="J293" s="6"/>
       <c r="K293" s="6"/>
@@ -14177,7 +14509,9 @@
         <v>0</v>
       </c>
       <c r="G294" s="6"/>
-      <c r="H294" s="6"/>
+      <c r="H294" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I294" s="6"/>
       <c r="J294" s="6"/>
       <c r="K294" s="6"/>
@@ -14203,7 +14537,9 @@
         <v>0</v>
       </c>
       <c r="G295" s="6"/>
-      <c r="H295" s="6"/>
+      <c r="H295" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I295" s="6"/>
       <c r="J295" s="6"/>
       <c r="K295" s="6"/>
@@ -14229,7 +14565,9 @@
         <v>0</v>
       </c>
       <c r="G296" s="6"/>
-      <c r="H296" s="6"/>
+      <c r="H296" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I296" s="6"/>
       <c r="J296" s="6"/>
       <c r="K296" s="6"/>
@@ -14255,7 +14593,9 @@
         <v>0</v>
       </c>
       <c r="G297" s="6"/>
-      <c r="H297" s="6"/>
+      <c r="H297" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I297" s="6"/>
       <c r="J297" s="6"/>
       <c r="K297" s="6"/>
@@ -14281,7 +14621,9 @@
         <v>0</v>
       </c>
       <c r="G298" s="6"/>
-      <c r="H298" s="6"/>
+      <c r="H298" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I298" s="6"/>
       <c r="J298" s="6"/>
       <c r="K298" s="6"/>
@@ -14307,7 +14649,9 @@
         <v>0</v>
       </c>
       <c r="G299" s="6"/>
-      <c r="H299" s="6"/>
+      <c r="H299" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I299" s="6"/>
       <c r="J299" s="6"/>
       <c r="K299" s="6"/>
@@ -14333,7 +14677,9 @@
         <v>0</v>
       </c>
       <c r="G300" s="6"/>
-      <c r="H300" s="6"/>
+      <c r="H300" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I300" s="6"/>
       <c r="J300" s="6"/>
       <c r="K300" s="6"/>
@@ -14359,7 +14705,9 @@
         <v>0</v>
       </c>
       <c r="G301" s="6"/>
-      <c r="H301" s="6"/>
+      <c r="H301" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I301" s="6"/>
       <c r="J301" s="6"/>
       <c r="K301" s="6"/>
@@ -14385,7 +14733,9 @@
         <v>0</v>
       </c>
       <c r="G302" s="6"/>
-      <c r="H302" s="6"/>
+      <c r="H302" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I302" s="6"/>
       <c r="J302" s="6"/>
       <c r="K302" s="6"/>
@@ -14411,7 +14761,9 @@
         <v>0</v>
       </c>
       <c r="G303" s="6"/>
-      <c r="H303" s="6"/>
+      <c r="H303" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I303" s="6"/>
       <c r="J303" s="6"/>
       <c r="K303" s="6"/>
@@ -14437,7 +14789,9 @@
         <v>0</v>
       </c>
       <c r="G304" s="6"/>
-      <c r="H304" s="6"/>
+      <c r="H304" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I304" s="6"/>
       <c r="J304" s="6"/>
       <c r="K304" s="6"/>
@@ -14463,7 +14817,9 @@
         <v>0</v>
       </c>
       <c r="G305" s="6"/>
-      <c r="H305" s="6"/>
+      <c r="H305" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I305" s="6"/>
       <c r="J305" s="6"/>
       <c r="K305" s="6"/>
@@ -14489,7 +14845,9 @@
         <v>0</v>
       </c>
       <c r="G306" s="6"/>
-      <c r="H306" s="6"/>
+      <c r="H306" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I306" s="6"/>
       <c r="J306" s="6"/>
       <c r="K306" s="6"/>
@@ -14515,7 +14873,9 @@
         <v>0</v>
       </c>
       <c r="G307" s="6"/>
-      <c r="H307" s="6"/>
+      <c r="H307" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I307" s="6"/>
       <c r="J307" s="6"/>
       <c r="K307" s="6"/>
@@ -14541,7 +14901,9 @@
         <v>0</v>
       </c>
       <c r="G308" s="6"/>
-      <c r="H308" s="6"/>
+      <c r="H308" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I308" s="6"/>
       <c r="J308" s="6"/>
       <c r="K308" s="6"/>
@@ -14567,7 +14929,9 @@
         <v>0</v>
       </c>
       <c r="G309" s="6"/>
-      <c r="H309" s="6"/>
+      <c r="H309" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I309" s="6"/>
       <c r="J309" s="6"/>
       <c r="K309" s="6"/>
@@ -14593,7 +14957,9 @@
         <v>0</v>
       </c>
       <c r="G310" s="6"/>
-      <c r="H310" s="6"/>
+      <c r="H310" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I310" s="6"/>
       <c r="J310" s="6"/>
       <c r="K310" s="6"/>
@@ -14619,7 +14985,9 @@
         <v>0</v>
       </c>
       <c r="G311" s="6"/>
-      <c r="H311" s="6"/>
+      <c r="H311" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I311" s="6"/>
       <c r="J311" s="6"/>
       <c r="K311" s="6"/>
@@ -14645,7 +15013,9 @@
         <v>0</v>
       </c>
       <c r="G312" s="6"/>
-      <c r="H312" s="6"/>
+      <c r="H312" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I312" s="6"/>
       <c r="J312" s="6"/>
       <c r="K312" s="6"/>
@@ -14671,7 +15041,9 @@
         <v>0</v>
       </c>
       <c r="G313" s="6"/>
-      <c r="H313" s="6"/>
+      <c r="H313" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I313" s="6"/>
       <c r="J313" s="6"/>
       <c r="K313" s="6"/>
@@ -14697,7 +15069,9 @@
         <v>0</v>
       </c>
       <c r="G314" s="6"/>
-      <c r="H314" s="6"/>
+      <c r="H314" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I314" s="6"/>
       <c r="J314" s="6"/>
       <c r="K314" s="6"/>
@@ -14723,7 +15097,9 @@
         <v>0</v>
       </c>
       <c r="G315" s="6"/>
-      <c r="H315" s="6"/>
+      <c r="H315" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I315" s="6"/>
       <c r="J315" s="6"/>
       <c r="K315" s="6"/>
@@ -14749,7 +15125,9 @@
         <v>0</v>
       </c>
       <c r="G316" s="6"/>
-      <c r="H316" s="6"/>
+      <c r="H316" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I316" s="6"/>
       <c r="J316" s="6"/>
       <c r="K316" s="6"/>
@@ -14775,7 +15153,9 @@
         <v>0</v>
       </c>
       <c r="G317" s="6"/>
-      <c r="H317" s="6"/>
+      <c r="H317" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I317" s="6"/>
       <c r="J317" s="6"/>
       <c r="K317" s="6"/>
@@ -14801,7 +15181,9 @@
         <v>0</v>
       </c>
       <c r="G318" s="6"/>
-      <c r="H318" s="6"/>
+      <c r="H318" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I318" s="6"/>
       <c r="J318" s="6"/>
       <c r="K318" s="6"/>
@@ -14827,7 +15209,9 @@
         <v>0</v>
       </c>
       <c r="G319" s="6"/>
-      <c r="H319" s="6"/>
+      <c r="H319" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I319" s="6"/>
       <c r="J319" s="6"/>
       <c r="K319" s="6"/>
@@ -14853,7 +15237,9 @@
         <v>0</v>
       </c>
       <c r="G320" s="6"/>
-      <c r="H320" s="6"/>
+      <c r="H320" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I320" s="6"/>
       <c r="J320" s="6"/>
       <c r="K320" s="6"/>
@@ -14879,7 +15265,9 @@
         <v>0</v>
       </c>
       <c r="G321" s="6"/>
-      <c r="H321" s="6"/>
+      <c r="H321" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I321" s="6"/>
       <c r="J321" s="6"/>
       <c r="K321" s="6"/>
@@ -14905,7 +15293,9 @@
         <v>0</v>
       </c>
       <c r="G322" s="6"/>
-      <c r="H322" s="6"/>
+      <c r="H322" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I322" s="6"/>
       <c r="J322" s="6"/>
       <c r="K322" s="6"/>
@@ -14931,7 +15321,9 @@
         <v>0</v>
       </c>
       <c r="G323" s="6"/>
-      <c r="H323" s="6"/>
+      <c r="H323" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I323" s="6"/>
       <c r="J323" s="6"/>
       <c r="K323" s="6"/>
@@ -14957,7 +15349,9 @@
         <v>0</v>
       </c>
       <c r="G324" s="6"/>
-      <c r="H324" s="6"/>
+      <c r="H324" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I324" s="6"/>
       <c r="J324" s="6"/>
       <c r="K324" s="6"/>
@@ -14983,7 +15377,9 @@
         <v>0</v>
       </c>
       <c r="G325" s="6"/>
-      <c r="H325" s="6"/>
+      <c r="H325" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I325" s="6"/>
       <c r="J325" s="6"/>
       <c r="K325" s="6"/>
@@ -15009,7 +15405,9 @@
         <v>0</v>
       </c>
       <c r="G326" s="6"/>
-      <c r="H326" s="6"/>
+      <c r="H326" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I326" s="6"/>
       <c r="J326" s="6"/>
       <c r="K326" s="6"/>
@@ -15035,7 +15433,9 @@
         <v>0</v>
       </c>
       <c r="G327" s="6"/>
-      <c r="H327" s="6"/>
+      <c r="H327" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I327" s="6"/>
       <c r="J327" s="6"/>
       <c r="K327" s="6"/>
@@ -15061,7 +15461,9 @@
         <v>0</v>
       </c>
       <c r="G328" s="6"/>
-      <c r="H328" s="6"/>
+      <c r="H328" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I328" s="6"/>
       <c r="J328" s="6"/>
       <c r="K328" s="6"/>
@@ -15087,7 +15489,9 @@
         <v>0</v>
       </c>
       <c r="G329" s="6"/>
-      <c r="H329" s="6"/>
+      <c r="H329" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I329" s="6"/>
       <c r="J329" s="6"/>
       <c r="K329" s="6"/>
@@ -15113,7 +15517,9 @@
         <v>0</v>
       </c>
       <c r="G330" s="6"/>
-      <c r="H330" s="6"/>
+      <c r="H330" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I330" s="6"/>
       <c r="J330" s="6"/>
       <c r="K330" s="6"/>
@@ -15139,7 +15545,9 @@
         <v>0</v>
       </c>
       <c r="G331" s="6"/>
-      <c r="H331" s="6"/>
+      <c r="H331" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I331" s="6"/>
       <c r="J331" s="6"/>
       <c r="K331" s="6"/>
@@ -15165,7 +15573,9 @@
         <v>0</v>
       </c>
       <c r="G332" s="6"/>
-      <c r="H332" s="6"/>
+      <c r="H332" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I332" s="6"/>
       <c r="J332" s="6"/>
       <c r="K332" s="6"/>
@@ -15191,7 +15601,9 @@
         <v>0</v>
       </c>
       <c r="G333" s="6"/>
-      <c r="H333" s="6"/>
+      <c r="H333" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I333" s="6"/>
       <c r="J333" s="6"/>
       <c r="K333" s="6"/>
@@ -15217,7 +15629,9 @@
         <v>0</v>
       </c>
       <c r="G334" s="6"/>
-      <c r="H334" s="6"/>
+      <c r="H334" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I334" s="6"/>
       <c r="J334" s="6"/>
       <c r="K334" s="6"/>
@@ -15243,7 +15657,9 @@
         <v>0</v>
       </c>
       <c r="G335" s="6"/>
-      <c r="H335" s="6"/>
+      <c r="H335" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I335" s="6"/>
       <c r="J335" s="6"/>
       <c r="K335" s="6"/>
@@ -15269,7 +15685,9 @@
         <v>0</v>
       </c>
       <c r="G336" s="6"/>
-      <c r="H336" s="6"/>
+      <c r="H336" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I336" s="6"/>
       <c r="J336" s="6"/>
       <c r="K336" s="6"/>
@@ -15295,7 +15713,9 @@
         <v>0</v>
       </c>
       <c r="G337" s="6"/>
-      <c r="H337" s="6"/>
+      <c r="H337" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I337" s="6"/>
       <c r="J337" s="6"/>
       <c r="K337" s="6"/>
@@ -15321,7 +15741,9 @@
         <v>0</v>
       </c>
       <c r="G338" s="6"/>
-      <c r="H338" s="6"/>
+      <c r="H338" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I338" s="6"/>
       <c r="J338" s="6"/>
       <c r="K338" s="6"/>
@@ -15347,7 +15769,9 @@
         <v>0</v>
       </c>
       <c r="G339" s="6"/>
-      <c r="H339" s="6"/>
+      <c r="H339" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I339" s="6"/>
       <c r="J339" s="6"/>
       <c r="K339" s="6"/>
@@ -15373,7 +15797,9 @@
         <v>0</v>
       </c>
       <c r="G340" s="6"/>
-      <c r="H340" s="6"/>
+      <c r="H340" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I340" s="6"/>
       <c r="J340" s="6"/>
       <c r="K340" s="6"/>
@@ -15399,7 +15825,9 @@
         <v>0</v>
       </c>
       <c r="G341" s="6"/>
-      <c r="H341" s="6"/>
+      <c r="H341" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I341" s="6"/>
       <c r="J341" s="6"/>
       <c r="K341" s="6"/>
@@ -15425,7 +15853,9 @@
         <v>0</v>
       </c>
       <c r="G342" s="6"/>
-      <c r="H342" s="6"/>
+      <c r="H342" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I342" s="6"/>
       <c r="J342" s="6"/>
       <c r="K342" s="6"/>
@@ -15451,7 +15881,9 @@
         <v>0</v>
       </c>
       <c r="G343" s="6"/>
-      <c r="H343" s="6"/>
+      <c r="H343" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I343" s="6"/>
       <c r="J343" s="6"/>
       <c r="K343" s="6"/>
@@ -15477,7 +15909,9 @@
         <v>0</v>
       </c>
       <c r="G344" s="6"/>
-      <c r="H344" s="6"/>
+      <c r="H344" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I344" s="6"/>
       <c r="J344" s="6"/>
       <c r="K344" s="6"/>
@@ -15503,7 +15937,9 @@
         <v>0</v>
       </c>
       <c r="G345" s="6"/>
-      <c r="H345" s="6"/>
+      <c r="H345" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I345" s="6"/>
       <c r="J345" s="6"/>
       <c r="K345" s="6"/>
@@ -15529,7 +15965,9 @@
         <v>0</v>
       </c>
       <c r="G346" s="6"/>
-      <c r="H346" s="6"/>
+      <c r="H346" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I346" s="6"/>
       <c r="J346" s="6"/>
       <c r="K346" s="6"/>
@@ -15555,7 +15993,9 @@
         <v>0</v>
       </c>
       <c r="G347" s="6"/>
-      <c r="H347" s="6"/>
+      <c r="H347" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I347" s="6"/>
       <c r="J347" s="6"/>
       <c r="K347" s="6"/>
@@ -15581,7 +16021,9 @@
         <v>0</v>
       </c>
       <c r="G348" s="6"/>
-      <c r="H348" s="6"/>
+      <c r="H348" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I348" s="6"/>
       <c r="J348" s="6"/>
       <c r="K348" s="6"/>
@@ -15607,7 +16049,9 @@
         <v>0</v>
       </c>
       <c r="G349" s="6"/>
-      <c r="H349" s="6"/>
+      <c r="H349" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I349" s="6"/>
       <c r="J349" s="6"/>
       <c r="K349" s="6"/>
@@ -15633,7 +16077,9 @@
         <v>0</v>
       </c>
       <c r="G350" s="6"/>
-      <c r="H350" s="6"/>
+      <c r="H350" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I350" s="6"/>
       <c r="J350" s="6"/>
       <c r="K350" s="6"/>
@@ -15659,7 +16105,9 @@
         <v>0</v>
       </c>
       <c r="G351" s="6"/>
-      <c r="H351" s="6"/>
+      <c r="H351" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I351" s="6"/>
       <c r="J351" s="6"/>
       <c r="K351" s="6"/>
@@ -15685,7 +16133,9 @@
         <v>0</v>
       </c>
       <c r="G352" s="6"/>
-      <c r="H352" s="6"/>
+      <c r="H352" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I352" s="6"/>
       <c r="J352" s="6"/>
       <c r="K352" s="6"/>
@@ -15711,7 +16161,9 @@
         <v>0</v>
       </c>
       <c r="G353" s="6"/>
-      <c r="H353" s="6"/>
+      <c r="H353" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I353" s="6"/>
       <c r="J353" s="6"/>
       <c r="K353" s="6"/>
@@ -15737,7 +16189,9 @@
         <v>0</v>
       </c>
       <c r="G354" s="6"/>
-      <c r="H354" s="6"/>
+      <c r="H354" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I354" s="6"/>
       <c r="J354" s="6"/>
       <c r="K354" s="6"/>
@@ -15763,7 +16217,9 @@
         <v>0</v>
       </c>
       <c r="G355" s="6"/>
-      <c r="H355" s="6"/>
+      <c r="H355" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I355" s="6"/>
       <c r="J355" s="6"/>
       <c r="K355" s="6"/>
@@ -15789,7 +16245,9 @@
         <v>0</v>
       </c>
       <c r="G356" s="6"/>
-      <c r="H356" s="6"/>
+      <c r="H356" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I356" s="6"/>
       <c r="J356" s="6"/>
       <c r="K356" s="6"/>
@@ -15815,7 +16273,9 @@
         <v>0</v>
       </c>
       <c r="G357" s="6"/>
-      <c r="H357" s="6"/>
+      <c r="H357" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I357" s="6"/>
       <c r="J357" s="6"/>
       <c r="K357" s="6"/>
@@ -15841,7 +16301,9 @@
         <v>0</v>
       </c>
       <c r="G358" s="6"/>
-      <c r="H358" s="6"/>
+      <c r="H358" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I358" s="6"/>
       <c r="J358" s="6"/>
       <c r="K358" s="6"/>
@@ -15867,7 +16329,9 @@
         <v>0</v>
       </c>
       <c r="G359" s="6"/>
-      <c r="H359" s="6"/>
+      <c r="H359" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I359" s="6"/>
       <c r="J359" s="6"/>
       <c r="K359" s="6"/>
@@ -15893,7 +16357,9 @@
         <v>0</v>
       </c>
       <c r="G360" s="6"/>
-      <c r="H360" s="6"/>
+      <c r="H360" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I360" s="6"/>
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
@@ -15919,7 +16385,9 @@
         <v>0</v>
       </c>
       <c r="G361" s="6"/>
-      <c r="H361" s="6"/>
+      <c r="H361" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I361" s="6"/>
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
@@ -15945,7 +16413,9 @@
         <v>0</v>
       </c>
       <c r="G362" s="6"/>
-      <c r="H362" s="6"/>
+      <c r="H362" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I362" s="6"/>
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
@@ -15971,7 +16441,9 @@
         <v>0</v>
       </c>
       <c r="G363" s="6"/>
-      <c r="H363" s="6"/>
+      <c r="H363" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I363" s="6"/>
       <c r="J363" s="6"/>
       <c r="K363" s="6"/>
@@ -15997,7 +16469,9 @@
         <v>0</v>
       </c>
       <c r="G364" s="6"/>
-      <c r="H364" s="6"/>
+      <c r="H364" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I364" s="6"/>
       <c r="J364" s="6"/>
       <c r="K364" s="6"/>
@@ -16023,7 +16497,9 @@
         <v>0</v>
       </c>
       <c r="G365" s="6"/>
-      <c r="H365" s="6"/>
+      <c r="H365" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I365" s="6"/>
       <c r="J365" s="6"/>
       <c r="K365" s="6"/>
@@ -16049,7 +16525,9 @@
         <v>0</v>
       </c>
       <c r="G366" s="6"/>
-      <c r="H366" s="6"/>
+      <c r="H366" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I366" s="6"/>
       <c r="J366" s="6"/>
       <c r="K366" s="6"/>
@@ -16075,7 +16553,9 @@
         <v>0</v>
       </c>
       <c r="G367" s="6"/>
-      <c r="H367" s="6"/>
+      <c r="H367" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I367" s="6"/>
       <c r="J367" s="6"/>
       <c r="K367" s="6"/>
@@ -16101,7 +16581,9 @@
         <v>0</v>
       </c>
       <c r="G368" s="6"/>
-      <c r="H368" s="6"/>
+      <c r="H368" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I368" s="6"/>
       <c r="J368" s="6"/>
       <c r="K368" s="6"/>
@@ -16127,7 +16609,9 @@
         <v>0</v>
       </c>
       <c r="G369" s="6"/>
-      <c r="H369" s="6"/>
+      <c r="H369" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I369" s="6"/>
       <c r="J369" s="6"/>
       <c r="K369" s="6"/>
@@ -16153,7 +16637,9 @@
         <v>0</v>
       </c>
       <c r="G370" s="6"/>
-      <c r="H370" s="6"/>
+      <c r="H370" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I370" s="6"/>
       <c r="J370" s="6"/>
       <c r="K370" s="6"/>
@@ -16179,7 +16665,9 @@
         <v>0</v>
       </c>
       <c r="G371" s="6"/>
-      <c r="H371" s="6"/>
+      <c r="H371" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I371" s="6"/>
       <c r="J371" s="6"/>
       <c r="K371" s="6"/>
@@ -16205,7 +16693,9 @@
         <v>0</v>
       </c>
       <c r="G372" s="6"/>
-      <c r="H372" s="6"/>
+      <c r="H372" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I372" s="6"/>
       <c r="J372" s="6"/>
       <c r="K372" s="6"/>
@@ -16231,7 +16721,9 @@
         <v>0</v>
       </c>
       <c r="G373" s="6"/>
-      <c r="H373" s="6"/>
+      <c r="H373" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I373" s="6"/>
       <c r="J373" s="6"/>
       <c r="K373" s="6"/>
@@ -16257,7 +16749,9 @@
         <v>0</v>
       </c>
       <c r="G374" s="6"/>
-      <c r="H374" s="6"/>
+      <c r="H374" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I374" s="6"/>
       <c r="J374" s="6"/>
       <c r="K374" s="6"/>
@@ -16283,7 +16777,9 @@
         <v>0</v>
       </c>
       <c r="G375" s="6"/>
-      <c r="H375" s="6"/>
+      <c r="H375" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I375" s="6"/>
       <c r="J375" s="6"/>
       <c r="K375" s="6"/>
@@ -16309,7 +16805,9 @@
         <v>0</v>
       </c>
       <c r="G376" s="6"/>
-      <c r="H376" s="6"/>
+      <c r="H376" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I376" s="6"/>
       <c r="J376" s="6"/>
       <c r="K376" s="6"/>
@@ -16335,7 +16833,9 @@
         <v>0</v>
       </c>
       <c r="G377" s="6"/>
-      <c r="H377" s="6"/>
+      <c r="H377" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I377" s="6"/>
       <c r="J377" s="6"/>
       <c r="K377" s="6"/>
@@ -16361,7 +16861,9 @@
         <v>0</v>
       </c>
       <c r="G378" s="6"/>
-      <c r="H378" s="6"/>
+      <c r="H378" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I378" s="6"/>
       <c r="J378" s="6"/>
       <c r="K378" s="6"/>
@@ -16387,7 +16889,9 @@
         <v>0</v>
       </c>
       <c r="G379" s="6"/>
-      <c r="H379" s="6"/>
+      <c r="H379" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I379" s="6"/>
       <c r="J379" s="6"/>
       <c r="K379" s="6"/>
@@ -16413,7 +16917,9 @@
         <v>0</v>
       </c>
       <c r="G380" s="6"/>
-      <c r="H380" s="6"/>
+      <c r="H380" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I380" s="6"/>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
@@ -16439,7 +16945,9 @@
         <v>0</v>
       </c>
       <c r="G381" s="6"/>
-      <c r="H381" s="6"/>
+      <c r="H381" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I381" s="6"/>
       <c r="J381" s="6"/>
       <c r="K381" s="6"/>
@@ -16465,7 +16973,9 @@
         <v>0</v>
       </c>
       <c r="G382" s="6"/>
-      <c r="H382" s="6"/>
+      <c r="H382" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I382" s="6"/>
       <c r="J382" s="6"/>
       <c r="K382" s="6"/>
@@ -16491,7 +17001,9 @@
         <v>0</v>
       </c>
       <c r="G383" s="6"/>
-      <c r="H383" s="6"/>
+      <c r="H383" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I383" s="6"/>
       <c r="J383" s="6"/>
       <c r="K383" s="6"/>
@@ -16517,7 +17029,9 @@
         <v>0</v>
       </c>
       <c r="G384" s="6"/>
-      <c r="H384" s="6"/>
+      <c r="H384" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I384" s="6"/>
       <c r="J384" s="6"/>
       <c r="K384" s="6"/>
@@ -16543,7 +17057,9 @@
         <v>0</v>
       </c>
       <c r="G385" s="6"/>
-      <c r="H385" s="6"/>
+      <c r="H385" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I385" s="6"/>
       <c r="J385" s="6"/>
       <c r="K385" s="6"/>
@@ -16569,7 +17085,9 @@
         <v>0</v>
       </c>
       <c r="G386" s="6"/>
-      <c r="H386" s="6"/>
+      <c r="H386" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I386" s="6"/>
       <c r="J386" s="6"/>
       <c r="K386" s="6"/>
@@ -16595,7 +17113,9 @@
         <v>0</v>
       </c>
       <c r="G387" s="6"/>
-      <c r="H387" s="6"/>
+      <c r="H387" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I387" s="6"/>
       <c r="J387" s="6"/>
       <c r="K387" s="6"/>
@@ -16621,7 +17141,9 @@
         <v>0</v>
       </c>
       <c r="G388" s="6"/>
-      <c r="H388" s="6"/>
+      <c r="H388" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I388" s="6"/>
       <c r="J388" s="6"/>
       <c r="K388" s="6"/>
@@ -16647,7 +17169,9 @@
         <v>0</v>
       </c>
       <c r="G389" s="6"/>
-      <c r="H389" s="6"/>
+      <c r="H389" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I389" s="6"/>
       <c r="J389" s="6"/>
       <c r="K389" s="6"/>
@@ -16673,7 +17197,9 @@
         <v>0</v>
       </c>
       <c r="G390" s="6"/>
-      <c r="H390" s="6"/>
+      <c r="H390" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I390" s="6"/>
       <c r="J390" s="6"/>
       <c r="K390" s="6"/>
@@ -16699,7 +17225,9 @@
         <v>0</v>
       </c>
       <c r="G391" s="6"/>
-      <c r="H391" s="6"/>
+      <c r="H391" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I391" s="6"/>
       <c r="J391" s="6"/>
       <c r="K391" s="6"/>
@@ -16725,7 +17253,9 @@
         <v>0</v>
       </c>
       <c r="G392" s="6"/>
-      <c r="H392" s="6"/>
+      <c r="H392" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I392" s="6"/>
       <c r="J392" s="6"/>
       <c r="K392" s="6"/>
@@ -16751,7 +17281,9 @@
         <v>0</v>
       </c>
       <c r="G393" s="6"/>
-      <c r="H393" s="6"/>
+      <c r="H393" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I393" s="6"/>
       <c r="J393" s="6"/>
       <c r="K393" s="6"/>
@@ -16777,7 +17309,9 @@
         <v>0</v>
       </c>
       <c r="G394" s="6"/>
-      <c r="H394" s="6"/>
+      <c r="H394" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I394" s="6"/>
       <c r="J394" s="6"/>
       <c r="K394" s="6"/>
@@ -16803,7 +17337,9 @@
         <v>0</v>
       </c>
       <c r="G395" s="6"/>
-      <c r="H395" s="6"/>
+      <c r="H395" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I395" s="6"/>
       <c r="J395" s="6"/>
       <c r="K395" s="6"/>
@@ -16829,7 +17365,9 @@
         <v>0</v>
       </c>
       <c r="G396" s="6"/>
-      <c r="H396" s="6"/>
+      <c r="H396" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I396" s="6"/>
       <c r="J396" s="6"/>
       <c r="K396" s="6"/>
@@ -16855,7 +17393,9 @@
         <v>0</v>
       </c>
       <c r="G397" s="6"/>
-      <c r="H397" s="6"/>
+      <c r="H397" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I397" s="6"/>
       <c r="J397" s="6"/>
       <c r="K397" s="6"/>
@@ -16881,7 +17421,9 @@
         <v>0</v>
       </c>
       <c r="G398" s="6"/>
-      <c r="H398" s="6"/>
+      <c r="H398" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I398" s="6"/>
       <c r="J398" s="6"/>
       <c r="K398" s="6"/>
@@ -16907,7 +17449,9 @@
         <v>0</v>
       </c>
       <c r="G399" s="6"/>
-      <c r="H399" s="6"/>
+      <c r="H399" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I399" s="6"/>
       <c r="J399" s="6"/>
       <c r="K399" s="6"/>
@@ -16933,7 +17477,9 @@
         <v>0</v>
       </c>
       <c r="G400" s="6"/>
-      <c r="H400" s="6"/>
+      <c r="H400" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I400" s="6"/>
       <c r="J400" s="6"/>
       <c r="K400" s="6"/>
@@ -16959,7 +17505,9 @@
         <v>0</v>
       </c>
       <c r="G401" s="6"/>
-      <c r="H401" s="6"/>
+      <c r="H401" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I401" s="6"/>
       <c r="J401" s="6"/>
       <c r="K401" s="6"/>
@@ -16985,7 +17533,9 @@
         <v>0</v>
       </c>
       <c r="G402" s="6"/>
-      <c r="H402" s="6"/>
+      <c r="H402" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I402" s="6"/>
       <c r="J402" s="6"/>
       <c r="K402" s="6"/>
@@ -17011,7 +17561,9 @@
         <v>0</v>
       </c>
       <c r="G403" s="6"/>
-      <c r="H403" s="6"/>
+      <c r="H403" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I403" s="6"/>
       <c r="J403" s="6"/>
       <c r="K403" s="6"/>
@@ -17037,7 +17589,9 @@
         <v>0</v>
       </c>
       <c r="G404" s="6"/>
-      <c r="H404" s="6"/>
+      <c r="H404" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I404" s="6"/>
       <c r="J404" s="6"/>
       <c r="K404" s="6"/>
@@ -17063,7 +17617,9 @@
         <v>0</v>
       </c>
       <c r="G405" s="6"/>
-      <c r="H405" s="6"/>
+      <c r="H405" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I405" s="6"/>
       <c r="J405" s="6"/>
       <c r="K405" s="6"/>
@@ -17089,7 +17645,9 @@
         <v>0</v>
       </c>
       <c r="G406" s="6"/>
-      <c r="H406" s="6"/>
+      <c r="H406" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I406" s="6"/>
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
@@ -17115,7 +17673,9 @@
         <v>0</v>
       </c>
       <c r="G407" s="6"/>
-      <c r="H407" s="6"/>
+      <c r="H407" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I407" s="6"/>
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
@@ -17141,7 +17701,9 @@
         <v>0</v>
       </c>
       <c r="G408" s="6"/>
-      <c r="H408" s="6"/>
+      <c r="H408" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I408" s="6"/>
       <c r="J408" s="6"/>
       <c r="K408" s="6"/>
@@ -17167,7 +17729,9 @@
         <v>0</v>
       </c>
       <c r="G409" s="6"/>
-      <c r="H409" s="6"/>
+      <c r="H409" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I409" s="6"/>
       <c r="J409" s="6"/>
       <c r="K409" s="6"/>
@@ -17193,7 +17757,9 @@
         <v>0</v>
       </c>
       <c r="G410" s="6"/>
-      <c r="H410" s="6"/>
+      <c r="H410" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I410" s="6"/>
       <c r="J410" s="6"/>
       <c r="K410" s="6"/>
@@ -17219,7 +17785,9 @@
         <v>0</v>
       </c>
       <c r="G411" s="6"/>
-      <c r="H411" s="6"/>
+      <c r="H411" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I411" s="6"/>
       <c r="J411" s="6"/>
       <c r="K411" s="6"/>
@@ -17245,7 +17813,9 @@
         <v>0</v>
       </c>
       <c r="G412" s="6"/>
-      <c r="H412" s="6"/>
+      <c r="H412" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I412" s="6"/>
       <c r="J412" s="6"/>
       <c r="K412" s="6"/>
@@ -17271,7 +17841,9 @@
         <v>0</v>
       </c>
       <c r="G413" s="6"/>
-      <c r="H413" s="6"/>
+      <c r="H413" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I413" s="6"/>
       <c r="J413" s="6"/>
       <c r="K413" s="6"/>
@@ -17297,7 +17869,9 @@
         <v>0</v>
       </c>
       <c r="G414" s="6"/>
-      <c r="H414" s="6"/>
+      <c r="H414" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I414" s="6"/>
       <c r="J414" s="6"/>
       <c r="K414" s="6"/>
@@ -17323,7 +17897,9 @@
         <v>0</v>
       </c>
       <c r="G415" s="6"/>
-      <c r="H415" s="6"/>
+      <c r="H415" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I415" s="6"/>
       <c r="J415" s="6"/>
       <c r="K415" s="6"/>
@@ -17349,7 +17925,9 @@
         <v>0</v>
       </c>
       <c r="G416" s="6"/>
-      <c r="H416" s="6"/>
+      <c r="H416" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I416" s="6"/>
       <c r="J416" s="6"/>
       <c r="K416" s="6"/>
@@ -17375,7 +17953,9 @@
         <v>0</v>
       </c>
       <c r="G417" s="6"/>
-      <c r="H417" s="6"/>
+      <c r="H417" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I417" s="6"/>
       <c r="J417" s="6"/>
       <c r="K417" s="6"/>
@@ -17401,7 +17981,9 @@
         <v>0</v>
       </c>
       <c r="G418" s="6"/>
-      <c r="H418" s="6"/>
+      <c r="H418" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I418" s="6"/>
       <c r="J418" s="6"/>
       <c r="K418" s="6"/>
@@ -17427,7 +18009,9 @@
         <v>0</v>
       </c>
       <c r="G419" s="6"/>
-      <c r="H419" s="6"/>
+      <c r="H419" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I419" s="6"/>
       <c r="J419" s="6"/>
       <c r="K419" s="6"/>
@@ -17453,7 +18037,9 @@
         <v>0</v>
       </c>
       <c r="G420" s="6"/>
-      <c r="H420" s="6"/>
+      <c r="H420" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I420" s="6"/>
       <c r="J420" s="6"/>
       <c r="K420" s="6"/>
@@ -17479,7 +18065,9 @@
         <v>0</v>
       </c>
       <c r="G421" s="6"/>
-      <c r="H421" s="6"/>
+      <c r="H421" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I421" s="6"/>
       <c r="J421" s="6"/>
       <c r="K421" s="6"/>
@@ -17505,7 +18093,9 @@
         <v>0</v>
       </c>
       <c r="G422" s="6"/>
-      <c r="H422" s="6"/>
+      <c r="H422" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I422" s="6"/>
       <c r="J422" s="6"/>
       <c r="K422" s="6"/>
@@ -17531,7 +18121,9 @@
         <v>0</v>
       </c>
       <c r="G423" s="6"/>
-      <c r="H423" s="6"/>
+      <c r="H423" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I423" s="6"/>
       <c r="J423" s="6"/>
       <c r="K423" s="6"/>
@@ -17557,7 +18149,9 @@
         <v>0</v>
       </c>
       <c r="G424" s="6"/>
-      <c r="H424" s="6"/>
+      <c r="H424" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I424" s="6"/>
       <c r="J424" s="6"/>
       <c r="K424" s="6"/>
@@ -17583,7 +18177,9 @@
         <v>0</v>
       </c>
       <c r="G425" s="6"/>
-      <c r="H425" s="6"/>
+      <c r="H425" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I425" s="6"/>
       <c r="J425" s="6"/>
       <c r="K425" s="6"/>
@@ -17609,7 +18205,9 @@
         <v>0</v>
       </c>
       <c r="G426" s="6"/>
-      <c r="H426" s="6"/>
+      <c r="H426" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I426" s="6"/>
       <c r="J426" s="6"/>
       <c r="K426" s="6"/>
@@ -17635,7 +18233,9 @@
         <v>0</v>
       </c>
       <c r="G427" s="6"/>
-      <c r="H427" s="6"/>
+      <c r="H427" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I427" s="6"/>
       <c r="J427" s="6"/>
       <c r="K427" s="6"/>
@@ -17661,7 +18261,9 @@
         <v>0</v>
       </c>
       <c r="G428" s="6"/>
-      <c r="H428" s="6"/>
+      <c r="H428" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I428" s="6"/>
       <c r="J428" s="6"/>
       <c r="K428" s="6"/>
@@ -17687,7 +18289,9 @@
         <v>0</v>
       </c>
       <c r="G429" s="6"/>
-      <c r="H429" s="6"/>
+      <c r="H429" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I429" s="6"/>
       <c r="J429" s="6"/>
       <c r="K429" s="6"/>
@@ -17713,7 +18317,9 @@
         <v>0</v>
       </c>
       <c r="G430" s="6"/>
-      <c r="H430" s="6"/>
+      <c r="H430" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I430" s="6"/>
       <c r="J430" s="6"/>
       <c r="K430" s="6"/>
@@ -17739,7 +18345,9 @@
         <v>0</v>
       </c>
       <c r="G431" s="6"/>
-      <c r="H431" s="6"/>
+      <c r="H431" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I431" s="6"/>
       <c r="J431" s="6"/>
       <c r="K431" s="6"/>
@@ -17765,7 +18373,9 @@
         <v>0</v>
       </c>
       <c r="G432" s="6"/>
-      <c r="H432" s="6"/>
+      <c r="H432" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I432" s="6"/>
       <c r="J432" s="6"/>
       <c r="K432" s="6"/>
@@ -17791,7 +18401,9 @@
         <v>0</v>
       </c>
       <c r="G433" s="6"/>
-      <c r="H433" s="6"/>
+      <c r="H433" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I433" s="6"/>
       <c r="J433" s="6"/>
       <c r="K433" s="6"/>
@@ -17817,7 +18429,9 @@
         <v>0</v>
       </c>
       <c r="G434" s="6"/>
-      <c r="H434" s="6"/>
+      <c r="H434" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I434" s="6"/>
       <c r="J434" s="6"/>
       <c r="K434" s="6"/>
@@ -17843,7 +18457,9 @@
         <v>0</v>
       </c>
       <c r="G435" s="6"/>
-      <c r="H435" s="6"/>
+      <c r="H435" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I435" s="6"/>
       <c r="J435" s="6"/>
       <c r="K435" s="6"/>
@@ -17869,7 +18485,9 @@
         <v>0</v>
       </c>
       <c r="G436" s="6"/>
-      <c r="H436" s="6"/>
+      <c r="H436" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I436" s="6"/>
       <c r="J436" s="6"/>
       <c r="K436" s="6"/>
@@ -17895,7 +18513,9 @@
         <v>0</v>
       </c>
       <c r="G437" s="6"/>
-      <c r="H437" s="6"/>
+      <c r="H437" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I437" s="6"/>
       <c r="J437" s="6"/>
       <c r="K437" s="6"/>
@@ -17921,7 +18541,9 @@
         <v>0</v>
       </c>
       <c r="G438" s="6"/>
-      <c r="H438" s="6"/>
+      <c r="H438" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I438" s="6"/>
       <c r="J438" s="6"/>
       <c r="K438" s="6"/>
@@ -17947,7 +18569,9 @@
         <v>0</v>
       </c>
       <c r="G439" s="6"/>
-      <c r="H439" s="6"/>
+      <c r="H439" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I439" s="6"/>
       <c r="J439" s="6"/>
       <c r="K439" s="6"/>
@@ -17973,7 +18597,9 @@
         <v>0</v>
       </c>
       <c r="G440" s="6"/>
-      <c r="H440" s="6"/>
+      <c r="H440" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I440" s="6"/>
       <c r="J440" s="6"/>
       <c r="K440" s="6"/>
@@ -17999,7 +18625,9 @@
         <v>0</v>
       </c>
       <c r="G441" s="6"/>
-      <c r="H441" s="6"/>
+      <c r="H441" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I441" s="6"/>
       <c r="J441" s="6"/>
       <c r="K441" s="6"/>
@@ -18025,7 +18653,9 @@
         <v>0</v>
       </c>
       <c r="G442" s="6"/>
-      <c r="H442" s="6"/>
+      <c r="H442" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I442" s="6"/>
       <c r="J442" s="6"/>
       <c r="K442" s="6"/>
@@ -18051,7 +18681,9 @@
         <v>0</v>
       </c>
       <c r="G443" s="6"/>
-      <c r="H443" s="6"/>
+      <c r="H443" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I443" s="6"/>
       <c r="J443" s="6"/>
       <c r="K443" s="6"/>
@@ -18077,7 +18709,9 @@
         <v>0</v>
       </c>
       <c r="G444" s="6"/>
-      <c r="H444" s="6"/>
+      <c r="H444" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I444" s="6"/>
       <c r="J444" s="6"/>
       <c r="K444" s="6"/>
@@ -18103,7 +18737,9 @@
         <v>0</v>
       </c>
       <c r="G445" s="6"/>
-      <c r="H445" s="6"/>
+      <c r="H445" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I445" s="6"/>
       <c r="J445" s="6"/>
       <c r="K445" s="6"/>
@@ -18129,7 +18765,9 @@
         <v>0</v>
       </c>
       <c r="G446" s="6"/>
-      <c r="H446" s="6"/>
+      <c r="H446" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I446" s="6"/>
       <c r="J446" s="6"/>
       <c r="K446" s="6"/>
@@ -18155,7 +18793,9 @@
         <v>0</v>
       </c>
       <c r="G447" s="6"/>
-      <c r="H447" s="6"/>
+      <c r="H447" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I447" s="6"/>
       <c r="J447" s="6"/>
       <c r="K447" s="6"/>
@@ -18181,7 +18821,9 @@
         <v>0</v>
       </c>
       <c r="G448" s="6"/>
-      <c r="H448" s="6"/>
+      <c r="H448" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I448" s="6"/>
       <c r="J448" s="6"/>
       <c r="K448" s="6"/>
@@ -18207,7 +18849,9 @@
         <v>0</v>
       </c>
       <c r="G449" s="6"/>
-      <c r="H449" s="6"/>
+      <c r="H449" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I449" s="6"/>
       <c r="J449" s="6"/>
       <c r="K449" s="6"/>
@@ -18233,7 +18877,9 @@
         <v>0</v>
       </c>
       <c r="G450" s="6"/>
-      <c r="H450" s="6"/>
+      <c r="H450" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I450" s="6"/>
       <c r="J450" s="6"/>
       <c r="K450" s="6"/>
@@ -18259,7 +18905,9 @@
         <v>0</v>
       </c>
       <c r="G451" s="6"/>
-      <c r="H451" s="6"/>
+      <c r="H451" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I451" s="6"/>
       <c r="J451" s="6"/>
       <c r="K451" s="6"/>
@@ -18285,7 +18933,9 @@
         <v>0</v>
       </c>
       <c r="G452" s="6"/>
-      <c r="H452" s="6"/>
+      <c r="H452" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I452" s="6"/>
       <c r="J452" s="6"/>
       <c r="K452" s="6"/>
@@ -18311,7 +18961,9 @@
         <v>0</v>
       </c>
       <c r="G453" s="6"/>
-      <c r="H453" s="6"/>
+      <c r="H453" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I453" s="6"/>
       <c r="J453" s="6"/>
       <c r="K453" s="6"/>
@@ -18337,7 +18989,9 @@
         <v>0</v>
       </c>
       <c r="G454" s="6"/>
-      <c r="H454" s="6"/>
+      <c r="H454" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I454" s="6"/>
       <c r="J454" s="6"/>
       <c r="K454" s="6"/>
@@ -18363,7 +19017,9 @@
         <v>0</v>
       </c>
       <c r="G455" s="6"/>
-      <c r="H455" s="6"/>
+      <c r="H455" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I455" s="6"/>
       <c r="J455" s="6"/>
       <c r="K455" s="6"/>
@@ -18387,7 +19043,9 @@
         <v>0</v>
       </c>
       <c r="G456" s="6"/>
-      <c r="H456" s="6"/>
+      <c r="H456" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I456" s="6"/>
       <c r="J456" s="6"/>
       <c r="K456" s="6"/>
@@ -18411,7 +19069,9 @@
         <v>0</v>
       </c>
       <c r="G457" s="6"/>
-      <c r="H457" s="6"/>
+      <c r="H457" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I457" s="6"/>
       <c r="J457" s="6"/>
       <c r="K457" s="6"/>
@@ -18435,7 +19095,9 @@
         <v>0</v>
       </c>
       <c r="G458" s="6"/>
-      <c r="H458" s="6"/>
+      <c r="H458" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I458" s="6"/>
       <c r="J458" s="6"/>
       <c r="K458" s="6"/>
@@ -18459,7 +19121,9 @@
         <v>0</v>
       </c>
       <c r="G459" s="6"/>
-      <c r="H459" s="6"/>
+      <c r="H459" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I459" s="6"/>
       <c r="J459" s="6"/>
       <c r="K459" s="6"/>
@@ -18483,7 +19147,9 @@
         <v>0</v>
       </c>
       <c r="G460" s="6"/>
-      <c r="H460" s="6"/>
+      <c r="H460" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I460" s="6"/>
       <c r="J460" s="6"/>
       <c r="K460" s="6"/>
@@ -18507,7 +19173,9 @@
         <v>0</v>
       </c>
       <c r="G461" s="6"/>
-      <c r="H461" s="6"/>
+      <c r="H461" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I461" s="6"/>
       <c r="J461" s="6"/>
       <c r="K461" s="6"/>
@@ -18531,7 +19199,9 @@
         <v>0</v>
       </c>
       <c r="G462" s="6"/>
-      <c r="H462" s="6"/>
+      <c r="H462" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I462" s="6"/>
       <c r="J462" s="6"/>
       <c r="K462" s="6"/>
@@ -18555,7 +19225,9 @@
         <v>0</v>
       </c>
       <c r="G463" s="6"/>
-      <c r="H463" s="6"/>
+      <c r="H463" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I463" s="6"/>
       <c r="J463" s="6"/>
       <c r="K463" s="6"/>
@@ -18579,7 +19251,9 @@
         <v>0</v>
       </c>
       <c r="G464" s="6"/>
-      <c r="H464" s="6"/>
+      <c r="H464" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I464" s="6"/>
       <c r="J464" s="6"/>
       <c r="K464" s="6"/>
@@ -18605,7 +19279,9 @@
         <v>0</v>
       </c>
       <c r="G465" s="6"/>
-      <c r="H465" s="6"/>
+      <c r="H465" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I465" s="6"/>
       <c r="J465" s="6"/>
       <c r="K465" s="6"/>
@@ -18631,7 +19307,9 @@
         <v>0</v>
       </c>
       <c r="G466" s="6"/>
-      <c r="H466" s="6"/>
+      <c r="H466" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I466" s="6"/>
       <c r="J466" s="6"/>
       <c r="K466" s="6"/>
@@ -18657,7 +19335,9 @@
         <v>0</v>
       </c>
       <c r="G467" s="6"/>
-      <c r="H467" s="6"/>
+      <c r="H467" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I467" s="6"/>
       <c r="J467" s="6"/>
       <c r="K467" s="6"/>
@@ -18683,7 +19363,9 @@
         <v>0</v>
       </c>
       <c r="G468" s="6"/>
-      <c r="H468" s="6"/>
+      <c r="H468" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I468" s="6"/>
       <c r="J468" s="6"/>
       <c r="K468" s="6"/>
@@ -18709,7 +19391,9 @@
         <v>0</v>
       </c>
       <c r="G469" s="6"/>
-      <c r="H469" s="6"/>
+      <c r="H469" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I469" s="6"/>
       <c r="J469" s="6"/>
       <c r="K469" s="6"/>
@@ -18735,7 +19419,9 @@
         <v>0</v>
       </c>
       <c r="G470" s="6"/>
-      <c r="H470" s="6"/>
+      <c r="H470" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I470" s="6"/>
       <c r="J470" s="6"/>
       <c r="K470" s="6"/>
@@ -18761,7 +19447,9 @@
         <v>0</v>
       </c>
       <c r="G471" s="6"/>
-      <c r="H471" s="6"/>
+      <c r="H471" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I471" s="6"/>
       <c r="J471" s="6"/>
       <c r="K471" s="6"/>
@@ -18787,7 +19475,9 @@
         <v>0</v>
       </c>
       <c r="G472" s="6"/>
-      <c r="H472" s="6"/>
+      <c r="H472" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I472" s="6"/>
       <c r="J472" s="6"/>
       <c r="K472" s="6"/>
@@ -18813,7 +19503,9 @@
         <v>0</v>
       </c>
       <c r="G473" s="6"/>
-      <c r="H473" s="6"/>
+      <c r="H473" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I473" s="6"/>
       <c r="J473" s="6"/>
       <c r="K473" s="6"/>
@@ -18839,7 +19531,9 @@
         <v>0</v>
       </c>
       <c r="G474" s="6"/>
-      <c r="H474" s="6"/>
+      <c r="H474" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I474" s="6"/>
       <c r="J474" s="6"/>
       <c r="K474" s="6"/>
@@ -18865,7 +19559,9 @@
         <v>0</v>
       </c>
       <c r="G475" s="6"/>
-      <c r="H475" s="6"/>
+      <c r="H475" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I475" s="6"/>
       <c r="J475" s="6"/>
       <c r="K475" s="6"/>
@@ -18891,7 +19587,9 @@
         <v>0</v>
       </c>
       <c r="G476" s="6"/>
-      <c r="H476" s="6"/>
+      <c r="H476" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I476" s="6"/>
       <c r="J476" s="6"/>
       <c r="K476" s="6"/>
@@ -18917,7 +19615,9 @@
         <v>0</v>
       </c>
       <c r="G477" s="6"/>
-      <c r="H477" s="6"/>
+      <c r="H477" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I477" s="6"/>
       <c r="J477" s="6"/>
       <c r="K477" s="6"/>
@@ -18943,7 +19643,9 @@
         <v>0</v>
       </c>
       <c r="G478" s="6"/>
-      <c r="H478" s="6"/>
+      <c r="H478" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I478" s="6"/>
       <c r="J478" s="6"/>
       <c r="K478" s="6"/>
@@ -18969,7 +19671,9 @@
         <v>0</v>
       </c>
       <c r="G479" s="6"/>
-      <c r="H479" s="6"/>
+      <c r="H479" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I479" s="6"/>
       <c r="J479" s="6"/>
       <c r="K479" s="6"/>
@@ -18995,7 +19699,9 @@
         <v>0</v>
       </c>
       <c r="G480" s="6"/>
-      <c r="H480" s="6"/>
+      <c r="H480" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I480" s="6"/>
       <c r="J480" s="6"/>
       <c r="K480" s="6"/>
@@ -19021,7 +19727,9 @@
         <v>0</v>
       </c>
       <c r="G481" s="6"/>
-      <c r="H481" s="6"/>
+      <c r="H481" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I481" s="6"/>
       <c r="J481" s="6"/>
       <c r="K481" s="6"/>
@@ -19045,7 +19753,9 @@
         <v>0</v>
       </c>
       <c r="G482" s="6"/>
-      <c r="H482" s="6"/>
+      <c r="H482" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I482" s="6"/>
       <c r="J482" s="6"/>
       <c r="K482" s="6"/>
@@ -19069,7 +19779,9 @@
         <v>0</v>
       </c>
       <c r="G483" s="6"/>
-      <c r="H483" s="6"/>
+      <c r="H483" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I483" s="6"/>
       <c r="J483" s="6"/>
       <c r="K483" s="6"/>
@@ -19093,7 +19805,9 @@
         <v>0</v>
       </c>
       <c r="G484" s="6"/>
-      <c r="H484" s="6"/>
+      <c r="H484" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I484" s="6"/>
       <c r="J484" s="6"/>
       <c r="K484" s="6"/>
@@ -19117,7 +19831,9 @@
         <v>0</v>
       </c>
       <c r="G485" s="6"/>
-      <c r="H485" s="6"/>
+      <c r="H485" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I485" s="6"/>
       <c r="J485" s="6"/>
       <c r="K485" s="6"/>
@@ -19143,7 +19859,9 @@
         <v>0</v>
       </c>
       <c r="G486" s="6"/>
-      <c r="H486" s="6"/>
+      <c r="H486" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I486" s="6"/>
       <c r="J486" s="6"/>
       <c r="K486" s="6"/>
@@ -19169,7 +19887,9 @@
         <v>0</v>
       </c>
       <c r="G487" s="6"/>
-      <c r="H487" s="6"/>
+      <c r="H487" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I487" s="6"/>
       <c r="J487" s="6"/>
       <c r="K487" s="6"/>
@@ -19195,7 +19915,9 @@
         <v>0</v>
       </c>
       <c r="G488" s="6"/>
-      <c r="H488" s="6"/>
+      <c r="H488" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I488" s="6"/>
       <c r="J488" s="6"/>
       <c r="K488" s="6"/>
@@ -19221,7 +19943,9 @@
         <v>0</v>
       </c>
       <c r="G489" s="6"/>
-      <c r="H489" s="6"/>
+      <c r="H489" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I489" s="6"/>
       <c r="J489" s="6"/>
       <c r="K489" s="6"/>
@@ -19247,7 +19971,9 @@
         <v>0</v>
       </c>
       <c r="G490" s="6"/>
-      <c r="H490" s="6"/>
+      <c r="H490" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I490" s="6"/>
       <c r="J490" s="6"/>
       <c r="K490" s="6"/>
@@ -19273,7 +19999,9 @@
         <v>0</v>
       </c>
       <c r="G491" s="6"/>
-      <c r="H491" s="6"/>
+      <c r="H491" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I491" s="6"/>
       <c r="J491" s="6"/>
       <c r="K491" s="6"/>
@@ -19299,7 +20027,9 @@
         <v>0</v>
       </c>
       <c r="G492" s="6"/>
-      <c r="H492" s="6"/>
+      <c r="H492" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I492" s="6"/>
       <c r="J492" s="6"/>
       <c r="K492" s="6"/>
@@ -19325,7 +20055,9 @@
         <v>0</v>
       </c>
       <c r="G493" s="6"/>
-      <c r="H493" s="6"/>
+      <c r="H493" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I493" s="6"/>
       <c r="J493" s="6"/>
       <c r="K493" s="6"/>
@@ -19351,7 +20083,9 @@
         <v>0</v>
       </c>
       <c r="G494" s="6"/>
-      <c r="H494" s="6"/>
+      <c r="H494" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I494" s="6"/>
       <c r="J494" s="6"/>
       <c r="K494" s="6"/>
@@ -19375,7 +20109,9 @@
         <v>0</v>
       </c>
       <c r="G495" s="6"/>
-      <c r="H495" s="6"/>
+      <c r="H495" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I495" s="6"/>
       <c r="J495" s="6"/>
       <c r="K495" s="6"/>
@@ -19399,7 +20135,9 @@
         <v>0</v>
       </c>
       <c r="G496" s="6"/>
-      <c r="H496" s="6"/>
+      <c r="H496" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I496" s="6"/>
       <c r="J496" s="6"/>
       <c r="K496" s="6"/>
@@ -19425,7 +20163,9 @@
         <v>0</v>
       </c>
       <c r="G497" s="6"/>
-      <c r="H497" s="6"/>
+      <c r="H497" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I497" s="6"/>
       <c r="J497" s="6"/>
       <c r="K497" s="6"/>
@@ -19451,7 +20191,9 @@
         <v>0</v>
       </c>
       <c r="G498" s="6"/>
-      <c r="H498" s="6"/>
+      <c r="H498" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I498" s="6"/>
       <c r="J498" s="6"/>
       <c r="K498" s="6"/>
@@ -19477,7 +20219,9 @@
         <v>0</v>
       </c>
       <c r="G499" s="6"/>
-      <c r="H499" s="6"/>
+      <c r="H499" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I499" s="6"/>
       <c r="J499" s="6"/>
       <c r="K499" s="6"/>
@@ -19503,7 +20247,9 @@
         <v>0</v>
       </c>
       <c r="G500" s="6"/>
-      <c r="H500" s="6"/>
+      <c r="H500" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I500" s="6"/>
       <c r="J500" s="6"/>
       <c r="K500" s="6"/>
@@ -19529,7 +20275,9 @@
         <v>0</v>
       </c>
       <c r="G501" s="6"/>
-      <c r="H501" s="6"/>
+      <c r="H501" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I501" s="6"/>
       <c r="J501" s="6"/>
       <c r="K501" s="6"/>
@@ -19555,7 +20303,9 @@
         <v>0</v>
       </c>
       <c r="G502" s="6"/>
-      <c r="H502" s="6"/>
+      <c r="H502" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I502" s="6"/>
       <c r="J502" s="6"/>
       <c r="K502" s="6"/>
@@ -19581,7 +20331,9 @@
         <v>0</v>
       </c>
       <c r="G503" s="6"/>
-      <c r="H503" s="6"/>
+      <c r="H503" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I503" s="6"/>
       <c r="J503" s="6"/>
       <c r="K503" s="6"/>
@@ -19607,7 +20359,9 @@
         <v>0</v>
       </c>
       <c r="G504" s="6"/>
-      <c r="H504" s="6"/>
+      <c r="H504" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I504" s="6"/>
       <c r="J504" s="6"/>
       <c r="K504" s="6"/>
@@ -19633,7 +20387,9 @@
         <v>0</v>
       </c>
       <c r="G505" s="6"/>
-      <c r="H505" s="6"/>
+      <c r="H505" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I505" s="6"/>
       <c r="J505" s="6"/>
       <c r="K505" s="6"/>
@@ -19659,7 +20415,9 @@
         <v>0</v>
       </c>
       <c r="G506" s="6"/>
-      <c r="H506" s="6"/>
+      <c r="H506" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I506" s="6"/>
       <c r="J506" s="6"/>
       <c r="K506" s="6"/>
@@ -19685,7 +20443,9 @@
         <v>0</v>
       </c>
       <c r="G507" s="6"/>
-      <c r="H507" s="6"/>
+      <c r="H507" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I507" s="6"/>
       <c r="J507" s="6"/>
       <c r="K507" s="6"/>
@@ -19711,7 +20471,9 @@
         <v>0</v>
       </c>
       <c r="G508" s="6"/>
-      <c r="H508" s="6"/>
+      <c r="H508" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I508" s="6"/>
       <c r="J508" s="6"/>
       <c r="K508" s="6"/>
@@ -19737,7 +20499,9 @@
         <v>0</v>
       </c>
       <c r="G509" s="6"/>
-      <c r="H509" s="6"/>
+      <c r="H509" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I509" s="6"/>
       <c r="J509" s="6"/>
       <c r="K509" s="6"/>
@@ -19761,7 +20525,9 @@
         <v>0</v>
       </c>
       <c r="G510" s="6"/>
-      <c r="H510" s="6"/>
+      <c r="H510" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I510" s="6"/>
       <c r="J510" s="6"/>
       <c r="K510" s="6"/>
@@ -19785,7 +20551,9 @@
         <v>0</v>
       </c>
       <c r="G511" s="6"/>
-      <c r="H511" s="6"/>
+      <c r="H511" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I511" s="6"/>
       <c r="J511" s="6"/>
       <c r="K511" s="6"/>
@@ -19809,7 +20577,9 @@
         <v>0</v>
       </c>
       <c r="G512" s="6"/>
-      <c r="H512" s="6"/>
+      <c r="H512" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I512" s="6"/>
       <c r="J512" s="6"/>
       <c r="K512" s="6"/>
@@ -19833,7 +20603,9 @@
         <v>0</v>
       </c>
       <c r="G513" s="6"/>
-      <c r="H513" s="6"/>
+      <c r="H513" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I513" s="6"/>
       <c r="J513" s="6"/>
       <c r="K513" s="6"/>
@@ -19857,7 +20629,9 @@
         <v>0</v>
       </c>
       <c r="G514" s="6"/>
-      <c r="H514" s="6"/>
+      <c r="H514" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I514" s="6"/>
       <c r="J514" s="6"/>
       <c r="K514" s="6"/>
@@ -19881,7 +20655,9 @@
         <v>0</v>
       </c>
       <c r="G515" s="6"/>
-      <c r="H515" s="6"/>
+      <c r="H515" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I515" s="6"/>
       <c r="J515" s="6"/>
       <c r="K515" s="6"/>
@@ -19905,7 +20681,9 @@
         <v>0</v>
       </c>
       <c r="G516" s="6"/>
-      <c r="H516" s="6"/>
+      <c r="H516" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I516" s="6"/>
       <c r="J516" s="6"/>
       <c r="K516" s="6"/>
@@ -19929,7 +20707,9 @@
         <v>0</v>
       </c>
       <c r="G517" s="6"/>
-      <c r="H517" s="6"/>
+      <c r="H517" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I517" s="6"/>
       <c r="J517" s="6"/>
       <c r="K517" s="6"/>
@@ -19953,7 +20733,9 @@
         <v>0</v>
       </c>
       <c r="G518" s="6"/>
-      <c r="H518" s="6"/>
+      <c r="H518" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I518" s="6"/>
       <c r="J518" s="6"/>
       <c r="K518" s="6"/>
@@ -19977,7 +20759,9 @@
         <v>0</v>
       </c>
       <c r="G519" s="6"/>
-      <c r="H519" s="6"/>
+      <c r="H519" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I519" s="6"/>
       <c r="J519" s="6"/>
       <c r="K519" s="6"/>
